--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
-  </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
   <si>
     <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
       <t xml:space="preserve">Подкатегория - Основная категория насоса(например: Вихревые насосы серии QB),
 Небольшое описание - например для чего нужен и так далее( в макете под названием на странице насоса),
 Категория - Основная категория насосов(например: Поверхностные (Садовые) насосы),
@@ -25,18 +28,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color indexed="2"/>
         <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">Очень важно, указываем перечиление моделей через запятую. как я показал в примере. В каком порядке указали модель в таком же порядке указываем и все остальные характеристики.
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <rFont val="Arial"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">Тут указываем характеристики насоса, если какой то характеритики нет, ничего в ячейку не ставим, если какой то характеристики не хватает, то добавляем название в столбец и заполняем.
 </t>
@@ -49,49 +52,53 @@
     <t>Подкатегории</t>
   </si>
   <si>
-    <t xml:space="preserve">Небольшое описание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основное фото</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дополнительные фото(через запятую)</t>
+    <t>Небольшое описание</t>
+  </si>
+  <si>
+    <t>Основное фото</t>
+  </si>
+  <si>
+    <t>Дополнительные фото(через запятую)</t>
   </si>
   <si>
     <t>Модель</t>
   </si>
   <si>
-    <t xml:space="preserve">Мощность, кВт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Электрическая сеть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ном. Производительность (м3/час)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Макс. Производительность м3/час</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Макс. производительность (л/мин)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ном. Напор (м)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Максимальный напор (м)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Максимальная глубина всасывания (м)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Присоединительный размер (дюйм)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Поверхностные (Садовые) насосы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии QB</t>
+    <t>Мощность, кВт</t>
+  </si>
+  <si>
+    <t>Электрическая сеть</t>
+  </si>
+  <si>
+    <t>Ном. Производительность (м3/час)</t>
+  </si>
+  <si>
+    <t>Макс. Производительность м3/час</t>
+  </si>
+  <si>
+    <t>Макс. производительность (л/мин)</t>
+  </si>
+  <si>
+    <t>Ном. Напор (м)</t>
+  </si>
+  <si>
+    <t>Максимальный напор (м)</t>
+  </si>
+  <si>
+    <t>Максимальная глубина всасывания (м)</t>
+  </si>
+  <si>
+    <t>Присоединительный размер (дюйм)</t>
+  </si>
+  <si>
+    <t>Поверхностные (Садовые) насосы</t>
+  </si>
+  <si>
+    <t>Насосы серии QB</t>
+  </si>
+  <si>
+    <t>Вихревые насосы серии QB предназначены для подачи чистой воды без абразивных примесей. 
+Они обеспечивают надежную и стабильную работу в бытовых и хозяйственных системах водоснабжения, где требуется чистая вода без твердых включений.</t>
   </si>
   <si>
     <t>nasos.jpg</t>
@@ -100,268 +107,268 @@
     <t>nasos1.jpg,nasos2.jpg,nasos3.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">ENSI QB60, ENSI QB70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37, 0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220В 50Гц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35, 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1" × 1"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии JS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI JS-60, ENSI JS-80, ENSI JS-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55, 0.75, 1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42, 45, 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38, 42, 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии JET-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI JET-S 60, ENSI JET-S 80, ENSI JET-S 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Погружные (Дренажные) насосы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии Q</t>
+    <t>ENSI QB60, ENSI QB70</t>
+  </si>
+  <si>
+    <t>0.37, 0.55</t>
+  </si>
+  <si>
+    <t>220В 50Гц</t>
+  </si>
+  <si>
+    <t>35, 50</t>
+  </si>
+  <si>
+    <t>1" × 1"</t>
+  </si>
+  <si>
+    <t>Насосы серии JS</t>
+  </si>
+  <si>
+    <t>ENSI JS-60, ENSI JS-80, ENSI JS-100</t>
+  </si>
+  <si>
+    <t>0.55, 0.75, 1.1</t>
+  </si>
+  <si>
+    <t>42, 45, 50</t>
+  </si>
+  <si>
+    <t>38, 42, 50</t>
+  </si>
+  <si>
+    <t>Насосы серии JET-S</t>
+  </si>
+  <si>
+    <t>ENSI JET-S 60, ENSI JET-S 80, ENSI JET-S 100</t>
+  </si>
+  <si>
+    <t>Погружные (Дренажные) насосы</t>
+  </si>
+  <si>
+    <t>Насосы серии Q</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI Q250 3, ENSI Q350 14-1, ENSI Q400 11, ENSI Q400 3А, ENSI Q400 51R, ENSI Q750 B11, ENSI Q750 B3, ENSI Q750 B54R, ENSI Q1100 B54R, ENSI Q1300 B101, ENSI Q1000 103-4Р  </t>
   </si>
   <si>
-    <t xml:space="preserve">0.25, 0.35, 0.4, 0.4, 0.4, 0.75, 0.75, 0.75, 1.1, 1.3, 1</t>
+    <t>0.25, 0.35, 0.4, 0.4, 0.4, 0.75, 0.75, 0.75, 1.1, 1.3, 1</t>
   </si>
   <si>
     <t xml:space="preserve">6, 10, 8, 8, 6.5, 8, 8,8, 10.5, 11, 40 </t>
   </si>
   <si>
-    <t xml:space="preserve">1", 11/4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии QDX</t>
+    <t>1", 11/4"</t>
+  </si>
+  <si>
+    <t>Насосы серии QDX</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI QDX1.5-16-0.37, ENSI QDX1.5-32-0.75, ENSI QDX 3-20-0.55, ENSI QDX 7-18-0.75,ENSI QDX 10-16-0.75, ENSI QDX 15-18-1.1 </t>
   </si>
   <si>
-    <t xml:space="preserve">0.37, 0.75, 0.55, 0.75, 0.75, 1.1</t>
+    <t>0.37, 0.75, 0.55, 0.75, 0.75, 1.1</t>
   </si>
   <si>
     <t xml:space="preserve">1.5, 1.5,  3, 7, 10, 15 </t>
   </si>
   <si>
-    <t xml:space="preserve">16, 32, 20, 18, 16, 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI V250F, ENSI V450F, ENSI V750F, ENSI V1100F-2, ENSI V1500F, ENSI V2200F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25, 0.45, 0.75, 1.1, 1.5, 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5, 19.5, 20.5, 26.5, 19, 45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5, 12.5, 14, 13, 20, 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1/4", 2", 2", 2", 2", 3"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии V с режущим механизмом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI V750GF, ENSI V1100GF, ENSI V1500GF, ENSI V2200GF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75, 1.1, 1.5, 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5, 15, 25, 36.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9, 12.5, 16, 19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1/2", 11/2", 2", 2 1/2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии ГНОМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI ГНОМ  50 WQ1.1, ENSI ГНОМ  50 WQ2.2, ENSI ГНОМ  50 WQ3.0, ENSI ГНОМ  50 WQ4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1, 2.2, 3, 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380В 50Гц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18, 24, 25, 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10, 16, 20, 25</t>
+    <t>16, 32, 20, 18, 16, 18</t>
+  </si>
+  <si>
+    <t>Насосы серии V</t>
+  </si>
+  <si>
+    <t>ENSI V250F, ENSI V450F, ENSI V750F, ENSI V1100F-2, ENSI V1500F, ENSI V2200F</t>
+  </si>
+  <si>
+    <t>0.25, 0.45, 0.75, 1.1, 1.5, 2.2</t>
+  </si>
+  <si>
+    <t>5, 19.5, 20.5, 26.5, 19, 45</t>
+  </si>
+  <si>
+    <t>7.5, 12.5, 14, 13, 20, 18</t>
+  </si>
+  <si>
+    <t>1 1/4", 2", 2", 2", 2", 3"</t>
+  </si>
+  <si>
+    <t>Насосы серии V с режущим механизмом</t>
+  </si>
+  <si>
+    <t>ENSI V750GF, ENSI V1100GF, ENSI V1500GF, ENSI V2200GF</t>
+  </si>
+  <si>
+    <t>0.75, 1.1, 1.5, 2.2</t>
+  </si>
+  <si>
+    <t>12.5, 15, 25, 36.5</t>
+  </si>
+  <si>
+    <t>9, 12.5, 16, 19</t>
+  </si>
+  <si>
+    <t>1 1/2", 11/2", 2", 2 1/2"</t>
+  </si>
+  <si>
+    <t>Насосы серии ГНОМ</t>
+  </si>
+  <si>
+    <t>ENSI ГНОМ  50 WQ1.1, ENSI ГНОМ  50 WQ2.2, ENSI ГНОМ  50 WQ3.0, ENSI ГНОМ  50 WQ4.0</t>
+  </si>
+  <si>
+    <t>1.1, 2.2, 3, 4</t>
+  </si>
+  <si>
+    <t>380В 50Гц</t>
+  </si>
+  <si>
+    <t>18, 24, 25, 30</t>
+  </si>
+  <si>
+    <t>10, 16, 20, 25</t>
   </si>
   <si>
     <t>2"</t>
   </si>
   <si>
-    <t xml:space="preserve">Насос скважинный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вентовые  3"</t>
+    <t>Насос скважинный</t>
+  </si>
+  <si>
+    <t>Вентовые  3"</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI 3QGD1-30-0.25, ENSI 3QGD1-45-0.37, ENSI 3QGD1.2-60-0.55                              </t>
   </si>
   <si>
-    <t xml:space="preserve">0.25, 0.37, 0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 2, 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 , 80, 110</t>
+    <t>0.25, 0.37, 0.55</t>
+  </si>
+  <si>
+    <t>2, 2, 2</t>
+  </si>
+  <si>
+    <t>60 , 80, 110</t>
   </si>
   <si>
     <t>1"</t>
   </si>
   <si>
-    <t xml:space="preserve">Однофазные  3"</t>
+    <t>Однофазные  3"</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI  TF3-1/30, ENSI  TF3-1/40, ENSI  TF3-1/60, ENSI  TF3-1/80, ENSI  TF3-1/110, ENSI  TF3-1/140, ENSI  TF3-1/180      </t>
   </si>
   <si>
-    <t xml:space="preserve">0.18 ,  0.25, 0.37, 0.55, 0.75, 1.1, 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 3, 3, 3, 3, 3, 3</t>
+    <t>0.18 ,  0.25, 0.37, 0.55, 0.75, 1.1, 1.5</t>
+  </si>
+  <si>
+    <t>3, 3, 3, 3, 3, 3, 3</t>
   </si>
   <si>
     <t xml:space="preserve">33 , 46 , 65 , 90 , 123 , 123 164 , 205  </t>
   </si>
   <si>
-    <t xml:space="preserve">Однофазные 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI TF4-3/60,  ENSI TF4-3/80, ENSI TF4-3/120, ENSI TF4-3/140,  ENSI TF4-3/160, ENSI TF4-3/190, ENSI TF4-3/220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,55,  0.75, 1.1 , 1.3, 1.5, 1.8, 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5, 5, 5, 5, 5, 5, 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60, 83, 121, 143, 166, 196, 226</t>
+    <t>Однофазные 4"</t>
+  </si>
+  <si>
+    <t>ENSI TF4-3/60,  ENSI TF4-3/80, ENSI TF4-3/120, ENSI TF4-3/140,  ENSI TF4-3/160, ENSI TF4-3/190, ENSI TF4-3/220</t>
+  </si>
+  <si>
+    <t>0,55,  0.75, 1.1 , 1.3, 1.5, 1.8, 2.2</t>
+  </si>
+  <si>
+    <t>5, 5, 5, 5, 5, 5, 5</t>
+  </si>
+  <si>
+    <t>60, 83, 121, 143, 166, 196, 226</t>
   </si>
   <si>
     <t>1¼"</t>
   </si>
   <si>
-    <t xml:space="preserve">Трехфазные 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI 4SР3-15, ENSI 4SР3-18,  ENSI 4SР3-22,  ENSI 4SР3-25,  ENSI 4SР3-29,  ENSI 4SР5-15, ENSI 4SР5-17, ENSI 4SР5-21, ENSI 4SР5-25, ENSI 4SР5-29, ENSI 4SР5-33, ENSI 4SР8-15, ENSI 4SР8-18, ENSI 4SР8-21, ENSI 4SР8-25, ENSI 4SР8-30, ENSI 4SР8-36,  ENSI 4SР14-13,  ENSI 4SР14-16,  ENSI 4SР14-18, ENSI 4SР14-21,  ENSI 4SР14-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92, 1.1, 1.3, 1.5, 1.8, 1.3, 1.5, 1.8, 2.2, 2.6, 3, 2.2, 3, 3.7, 4, 5, 5.5, 4, 5, 5.5, 6.8, 7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 3, 3, 3, 3, 5, 5, 5, 5, 5, 5, 8, 8, 8, 8, 8, 8, 14, 14, 14, 14, 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94, 113, 138, 157, 182, 95, 108, 134, 159, 185, 210, 95, 114, 133, 159, 191, 229, 89, 110, 124, 144, 165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трехфазные 5-6"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI 5SR10/13, ENSI 5SR10/16, ENSI 6SR10/08, ENSI 6SR10/11, ENSI 6SR10/14, ENSI 6SR10/14, ENSI 6SR10/20, ENSI 6SR18/10, ENSI 6SR18/15, ENSI 6SR30/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 4, 4, 5.5, 7.5, 11, 7.5, 11, 11</t>
+    <t>Трехфазные 4"</t>
+  </si>
+  <si>
+    <t>ENSI 4SР3-15, ENSI 4SР3-18,  ENSI 4SР3-22,  ENSI 4SР3-25,  ENSI 4SР3-29,  ENSI 4SР5-15, ENSI 4SР5-17, ENSI 4SР5-21, ENSI 4SР5-25, ENSI 4SР5-29, ENSI 4SР5-33, ENSI 4SР8-15, ENSI 4SР8-18, ENSI 4SР8-21, ENSI 4SР8-25, ENSI 4SР8-30, ENSI 4SР8-36,  ENSI 4SР14-13,  ENSI 4SР14-16,  ENSI 4SР14-18, ENSI 4SР14-21,  ENSI 4SР14-24</t>
+  </si>
+  <si>
+    <t>0.92, 1.1, 1.3, 1.5, 1.8, 1.3, 1.5, 1.8, 2.2, 2.6, 3, 2.2, 3, 3.7, 4, 5, 5.5, 4, 5, 5.5, 6.8, 7.5</t>
+  </si>
+  <si>
+    <t>3, 3, 3, 3, 3, 5, 5, 5, 5, 5, 5, 8, 8, 8, 8, 8, 8, 14, 14, 14, 14, 14</t>
+  </si>
+  <si>
+    <t>94, 113, 138, 157, 182, 95, 108, 134, 159, 185, 210, 95, 114, 133, 159, 191, 229, 89, 110, 124, 144, 165</t>
+  </si>
+  <si>
+    <t>Трехфазные 5-6"</t>
+  </si>
+  <si>
+    <t>ENSI 5SR10/13, ENSI 5SR10/16, ENSI 6SR10/08, ENSI 6SR10/11, ENSI 6SR10/14, ENSI 6SR10/14, ENSI 6SR10/20, ENSI 6SR18/10, ENSI 6SR18/15, ENSI 6SR30/11</t>
+  </si>
+  <si>
+    <t>3, 4, 4, 5.5, 7.5, 11, 7.5, 11, 11</t>
   </si>
   <si>
     <t xml:space="preserve"> 10, 10, 10, 10, 10, 10, 10, 18,18,30</t>
   </si>
   <si>
-    <t xml:space="preserve">115, 142, 109, 149, 204, 272, 142, 213, 158</t>
+    <t>115, 142, 109, 149, 204, 272, 142, 213, 158</t>
   </si>
   <si>
     <t>3"</t>
   </si>
   <si>
-    <t xml:space="preserve">Горизонтальные многоступенчатые насосы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии HMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI HMC 90-5SH, ENSI HMC 90-6SH, ENSI HMC 170-4SH, ENSI HMC 170-5SH, ENSI HMC 170-6SH</t>
+    <t>Горизонтальные многоступенчатые насосы</t>
+  </si>
+  <si>
+    <t>Насосы серии HMC</t>
+  </si>
+  <si>
+    <t>ENSI HMC 90-5SH, ENSI HMC 90-6SH, ENSI HMC 170-4SH, ENSI HMC 170-5SH, ENSI HMC 170-6SH</t>
   </si>
   <si>
     <t xml:space="preserve">1, 1.3, 1.35, 1.65, 2.1 </t>
   </si>
   <si>
-    <t xml:space="preserve">90, 90, 170, 170, 170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58, 70, 52, 65, 78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8, 8, 8, 8, 8</t>
+    <t>90, 90, 170, 170, 170</t>
+  </si>
+  <si>
+    <t>58, 70, 52, 65, 78</t>
+  </si>
+  <si>
+    <t>8, 8, 8, 8, 8</t>
   </si>
   <si>
     <t xml:space="preserve">1" × 1", 1" × 1", 1¼" × 1¼", 1¼" × 1¼", 1¼" × 1¼", </t>
   </si>
   <si>
-    <t xml:space="preserve">Насосы серии CMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI CMH 2-30, ENSI CMH 2-40, ENSI CMH 2-50, ENSI CMH 2-50Т, ENSI CMH 2-60, ENSI CMH 4-30, ENSI CMH 4-30Т, ENSI CMH 4-40, ENSI CMH 4-50, ENSI CMH 4-50Т, ENSI CMH 4-60, ENSI CMH 4-60T, ENSI CMH 8-30В, ENSI CMH 8-40В, ENSI CMH 8-40ВТ, ENSI CMH 8-50ВT, ENSI CMH 8-60ВT, ENSI CMH20-20ВТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37, 0.55, 0.55, 0.55, 0.75, 0.75, 0.75, 0.75, 1, 1, 1.1, 1.1, 1.1, 1.5, 1.5, 2.2, 3, 1.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 380В 50Гц, 380В 50Гц, 380В 50Гц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 2, 2, 2, 2, 4, 4, 4, 4, 4, 4, 4, 8, 8, 8, 8, 8, 20</t>
+    <t>Насосы серии CMH</t>
+  </si>
+  <si>
+    <t>ENSI CMH 2-30, ENSI CMH 2-40, ENSI CMH 2-50, ENSI CMH 2-50Т, ENSI CMH 2-60, ENSI CMH 4-30, ENSI CMH 4-30Т, ENSI CMH 4-40, ENSI CMH 4-50, ENSI CMH 4-50Т, ENSI CMH 4-60, ENSI CMH 4-60T, ENSI CMH 8-30В, ENSI CMH 8-40В, ENSI CMH 8-40ВТ, ENSI CMH 8-50ВT, ENSI CMH 8-60ВT, ENSI CMH20-20ВТ</t>
+  </si>
+  <si>
+    <t>0.37, 0.55, 0.55, 0.55, 0.75, 0.75, 0.75, 0.75, 1, 1, 1.1, 1.1, 1.1, 1.5, 1.5, 2.2, 3, 1.85</t>
+  </si>
+  <si>
+    <t>220В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 380В 50Гц, 220В 50Гц, 220В 50Гц, 380В 50Гц, 380В 50Гц, 380В 50Гц, 380В 50Гц</t>
+  </si>
+  <si>
+    <t>2, 2, 2, 2, 2, 4, 4, 4, 4, 4, 4, 4, 8, 8, 8, 8, 8, 20</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">21, 28, 35, 35, 42, 22, 22, 30, 38, 38, 45, 45, 25, 37, 37, 46.5, 52, 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1" × 1", 1" × 1", 1" × 1", 1" × 1", 1" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 2" × 2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Насосы серии CMI</t>
+    <t>21, 28, 35, 35, 42, 22, 22, 30, 38, 38, 45, 45, 25, 37, 37, 46.5, 52, 20</t>
+  </si>
+  <si>
+    <t>1" × 1", 1" × 1", 1" × 1", 1" × 1", 1" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1¼" × 1", 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 1½" × 1¼, 2" × 2"</t>
+  </si>
+  <si>
+    <t>Насосы серии CMI</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI CMI 1-2, ENSI CMI 1-3, ENSI CMI 1-4, </t>
@@ -370,41 +377,40 @@
     <t xml:space="preserve">0.25, 0.25, 0.37, </t>
   </si>
   <si>
-    <t xml:space="preserve">1, 1, 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18, 25, 33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1" × 1", 1" × 1", 1" × 1"</t>
+    <t>1, 1, 1</t>
+  </si>
+  <si>
+    <t>18, 25, 33</t>
+  </si>
+  <si>
+    <t>1" × 1", 1" × 1", 1" × 1"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <fonts count="4">
     <font>
-      <sz val="10.000000"/>
-      <color indexed="64"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <color theme="1"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -412,375 +418,85 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="3"/>
-        <bgColor indexed="3"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -837,7 +553,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -863,7 +579,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -915,28 +631,16 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -952,7 +656,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -982,690 +686,1287 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="38.28515625"/>
-    <col customWidth="1" min="2" max="2" width="34.140625"/>
-    <col customWidth="1" min="3" max="3" width="16"/>
-    <col customWidth="1" min="4" max="4" width="15.42578125"/>
-    <col customWidth="1" min="5" max="5" width="17.85546875"/>
-    <col customWidth="1" min="6" max="6" width="46.7109375"/>
-    <col customWidth="1" min="7" max="7" width="21.5703125"/>
-    <col customWidth="1" min="8" max="8" width="21.85546875"/>
-    <col customWidth="1" min="9" max="9" width="36.140625"/>
-    <col customWidth="1" min="10" max="10" width="35.140625"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="35.5703125"/>
-    <col customWidth="1" min="12" max="12" width="16.42578125"/>
-    <col customWidth="1" min="13" max="13" width="26.140625"/>
-    <col customWidth="1" min="14" max="14" width="40"/>
-    <col customWidth="1" min="15" max="15" width="37.28515625"/>
+    <col customWidth="1" min="1" max="1" width="33.5"/>
+    <col customWidth="1" min="2" max="2" width="29.88"/>
+    <col customWidth="1" min="3" max="3" width="14.0"/>
+    <col customWidth="1" min="4" max="4" width="17.75"/>
+    <col customWidth="1" min="5" max="5" width="35.63"/>
+    <col customWidth="1" min="6" max="6" width="40.88"/>
+    <col customWidth="1" min="7" max="7" width="18.88"/>
+    <col customWidth="1" min="8" max="8" width="19.13"/>
+    <col customWidth="1" min="9" max="9" width="31.63"/>
+    <col customWidth="1" min="10" max="10" width="30.75"/>
+    <col customWidth="1" min="11" max="11" width="31.13"/>
+    <col customWidth="1" min="12" max="12" width="14.38"/>
+    <col customWidth="1" min="13" max="13" width="22.88"/>
+    <col customWidth="1" min="14" max="14" width="35.0"/>
+    <col customWidth="1" min="15" max="15" width="32.63"/>
+    <col customWidth="1" min="16" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="110.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+    <row r="3" ht="21.0" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" ht="21.0" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="7">
-        <v>8</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="7">
-        <v>9</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" s="8" customFormat="1" ht="21.75" customHeight="1">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+    </row>
+    <row r="5" ht="21.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N5" s="9">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" s="8" customFormat="1" ht="59.25" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" ht="59.25" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" s="8" customFormat="1" ht="42" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="B7" s="8" t="s">
-        <v>38</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>41</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" s="8" customFormat="1" ht="26.25" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+    </row>
+    <row r="8" ht="26.25" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>43</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I8" s="8"/>
       <c r="J8" s="8" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
       <c r="M8" s="8" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N8" s="8"/>
       <c r="O8" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" s="8" customFormat="1" ht="31.5" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I9" s="8"/>
       <c r="J9" s="8" t="s">
-        <v>52</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
       <c r="M9" s="8" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="N9" s="8"/>
       <c r="O9" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" s="8" customFormat="1" ht="39.75" customHeight="1">
+        <v>55</v>
+      </c>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>55</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>59</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
-        <v>60</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" s="10" customFormat="1" ht="41.25" customHeight="1">
+        <v>62</v>
+      </c>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+    </row>
+    <row r="11" ht="41.25" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K11" s="8"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" s="8" customFormat="1" ht="42" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>22</v>
+        <v>72</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
       <c r="M12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" s="10" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+    </row>
+    <row r="13" ht="38.25" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K13" s="7"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" s="10" customFormat="1" ht="96.75" customHeight="1">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+    </row>
+    <row r="14" ht="96.75" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-    </row>
-    <row r="15" s="10" customFormat="1" ht="51.75" customHeight="1">
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+    </row>
+    <row r="15" ht="51.75" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N15" s="8"/>
       <c r="O15" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" s="8" customFormat="1" ht="49.5" customHeight="1">
+        <v>91</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+    </row>
+    <row r="16" ht="49.5" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" s="8" customFormat="1" ht="123.75" customHeight="1">
+        <v>99</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+    </row>
+    <row r="17" ht="123.75" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="8"/>
+        <v>100</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L17" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+    </row>
+    <row r="18" ht="45.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="8"/>
-      <c r="O17" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" s="8" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="F18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="L18" s="8" t="s">
-        <v>111</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
       <c r="O18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="1" ht="105.75" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="21" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="22" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="23" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="24" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="25" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="26" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="27" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="28" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="29" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="30" s="11" customFormat="1" ht="105.75" customHeight="1"/>
-    <row r="31" s="11" customFormat="1" ht="105.75" customHeight="1"/>
+        <v>113</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+    </row>
+    <row r="19" ht="105.75" customHeight="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+    </row>
+    <row r="20" ht="105.75" customHeight="1">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+    </row>
+    <row r="21" ht="105.75" customHeight="1">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
+    </row>
+    <row r="22" ht="105.75" customHeight="1">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
+    </row>
+    <row r="23" ht="105.75" customHeight="1">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+    </row>
+    <row r="24" ht="105.75" customHeight="1">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+    </row>
+    <row r="25" ht="105.75" customHeight="1">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
+    </row>
+    <row r="26" ht="105.75" customHeight="1">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
+    </row>
+    <row r="27" ht="105.75" customHeight="1">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
+    </row>
+    <row r="28" ht="105.75" customHeight="1">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
+    </row>
+    <row r="29" ht="105.75" customHeight="1">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
+    </row>
+    <row r="30" ht="105.75" customHeight="1">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+    </row>
+    <row r="31" ht="105.75" customHeight="1">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+    </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
@@ -2631,14 +2932,13 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,85 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Подкатегория - Основная категория насоса(например: Вихревые насосы серии QB),
-Небольшое описание - например для чего нужен и так далее( в макете под названием на странице насоса),
-Категория - Основная категория насосов(например: Поверхностные (Садовые) насосы),
-Основное фото - Тут указываем название фотографии с расширением(обязательно).например nasos.jpg, nasos.png, 1.webp, 1.png и так далее,
-Дополнительные фотографии -  Тут через запятую указываем фотографии через запятую если их должно быть больше 1 на странице. например(nasos.jpg, nasos.png, 1.webp, 1.png),
-Модель,мощность, подача и так далее -  </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Очень важно, указываем перечиление моделей через запятую. как я показал в примере. В каком порядке указали модель в таком же порядке указываем и все остальные характеристики.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Тут указываем характеристики насоса, если какой то характеритики нет, ничего в ячейку не ставим, если какой то характеристики не хватает, то добавляем название в столбец и заполняем.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Категория</t>
-  </si>
-  <si>
-    <t>Подкатегории</t>
-  </si>
-  <si>
-    <t>Небольшое описание</t>
-  </si>
-  <si>
-    <t>Основное фото</t>
-  </si>
-  <si>
-    <t>Дополнительные фото(через запятую)</t>
-  </si>
-  <si>
-    <t>Модель</t>
-  </si>
-  <si>
-    <t>Мощность, кВт</t>
-  </si>
-  <si>
-    <t>Электрическая сеть</t>
-  </si>
-  <si>
-    <t>Ном. Производительность (м3/час)</t>
-  </si>
-  <si>
-    <t>Макс. Производительность м3/час</t>
-  </si>
-  <si>
-    <t>Макс. производительность (л/мин)</t>
-  </si>
-  <si>
-    <t>Ном. Напор (м)</t>
-  </si>
-  <si>
-    <t>Максимальный напор (м)</t>
-  </si>
-  <si>
-    <t>Максимальная глубина всасывания (м)</t>
-  </si>
-  <si>
-    <t>Присоединительный размер (дюйм)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
   <si>
     <t>Поверхностные (Садовые) насосы</t>
   </si>
@@ -390,7 +312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -403,28 +325,17 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -447,40 +358,35 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -715,56 +621,93 @@
     <col customWidth="1" min="16" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="110.25" customHeight="1">
+    <row r="1" ht="21.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" ht="21.0" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -778,1196 +721,1098 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="21.75" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="59.25" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="O3" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-    </row>
-    <row r="4" ht="21.0" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="H5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6" ht="26.25" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="H6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
-    </row>
-    <row r="6" ht="59.25" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="N6" s="5"/>
+      <c r="O6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8" t="s">
+      <c r="H7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="N7" s="5"/>
+      <c r="O7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8" t="s">
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+    </row>
+    <row r="8" ht="39.75" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="G8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-    </row>
-    <row r="8" ht="26.25" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="I8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8" t="s">
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+    </row>
+    <row r="9" ht="41.25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8" t="s">
+      <c r="C9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="G9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
+      <c r="H9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="K9" s="5"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8" t="s">
+      <c r="N9" s="5"/>
+      <c r="O9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8" t="s">
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+    </row>
+    <row r="10" ht="42.0" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8" t="s">
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="G10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
+      <c r="H10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="K10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="N10" s="3"/>
+      <c r="O10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+    </row>
+    <row r="11" ht="38.25" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8" t="s">
+      <c r="G11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="9" t="s">
+      <c r="H11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-    </row>
-    <row r="11" ht="41.25" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="K11" s="4"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+    </row>
+    <row r="12" ht="96.75" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
+      <c r="G12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="8" t="s">
+      <c r="H12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+    </row>
+    <row r="13" ht="51.75" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="8" t="s">
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
+      <c r="H13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8" t="s">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-    </row>
-    <row r="13" ht="38.25" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="N13" s="5"/>
+      <c r="O13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8" t="s">
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+    </row>
+    <row r="14" ht="49.5" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="8" t="s">
+      <c r="G14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6" t="s">
+      <c r="H14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-    </row>
-    <row r="14" ht="96.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="L14" s="5"/>
+      <c r="M14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="N14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="O14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+    </row>
+    <row r="15" ht="123.75" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="8" t="s">
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-    </row>
-    <row r="15" ht="51.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="G15" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="H15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="I15" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="8" t="s">
+      <c r="L15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8" t="s">
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-    </row>
-    <row r="16" ht="49.5" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+    </row>
+    <row r="16" ht="45.75" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8" t="s">
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-    </row>
-    <row r="17" ht="123.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+    </row>
+    <row r="17" ht="105.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>104</v>
-      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>106</v>
-      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-      <c r="O17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
-    </row>
-    <row r="18" ht="45.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+    </row>
+    <row r="18" ht="105.75" customHeight="1">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
     </row>
     <row r="19" ht="105.75" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
     </row>
     <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
     </row>
     <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
     </row>
     <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
     </row>
     <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
     </row>
     <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
     </row>
     <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
     </row>
     <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-    </row>
-    <row r="30" ht="105.75" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-    </row>
-    <row r="31" ht="105.75" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-    </row>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2930,12 +2775,7 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
-  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,7 +11,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Подкатегория - Основная категория насоса(например: Вихревые насосы серии QB),
+Небольшое описание - например для чего нужен и так далее( в макете под названием на странице насоса),
+Категория - Основная категория насосов(например: Поверхностные (Садовые) насосы),
+Основное фото - Тут указываем название фотографии с расширением(обязательно).например nasos.jpg, nasos.png, 1.webp, 1.png и так далее,
+Дополнительные фотографии -  Тут через запятую указываем фотографии через запятую если их должно быть больше 1 на странице. например(nasos.jpg, nasos.png, 1.webp, 1.png),
+Модель,мощность, подача и так далее -  </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Очень важно, указываем перечиление моделей через запятую. как я показал в примере. В каком порядке указали модель в таком же порядке указываем и все остальные характеристики.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Тут указываем характеристики насоса, если какой то характеритики нет, ничего в ячейку не ставим, если какой то характеристики не хватает, то добавляем название в столбец и заполняем.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Подкатегории</t>
+  </si>
+  <si>
+    <t>Небольшое описание</t>
+  </si>
+  <si>
+    <t>Основное фото</t>
+  </si>
+  <si>
+    <t>Дополнительные фото(через запятую)</t>
+  </si>
+  <si>
+    <t>Модель</t>
+  </si>
+  <si>
+    <t>Мощность, кВт</t>
+  </si>
+  <si>
+    <t>Электрическая сеть</t>
+  </si>
+  <si>
+    <t>Ном. Производительность (м3/час)</t>
+  </si>
+  <si>
+    <t>Макс. Производительность м3/час</t>
+  </si>
+  <si>
+    <t>Макс. производительность (л/мин)</t>
+  </si>
+  <si>
+    <t>Ном. Напор (м)</t>
+  </si>
+  <si>
+    <t>Максимальный напор (м)</t>
+  </si>
+  <si>
+    <t>Максимальная глубина всасывания (м)</t>
+  </si>
+  <si>
+    <t>Присоединительный размер (дюйм)</t>
+  </si>
   <si>
     <t>Поверхностные (Садовые) насосы</t>
   </si>
@@ -312,7 +390,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -325,17 +403,28 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -358,35 +447,40 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -621,93 +715,56 @@
     <col customWidth="1" min="16" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.0" customHeight="1">
+    <row r="1" ht="110.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-    </row>
-    <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4">
-        <v>9.0</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -721,1098 +778,1196 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+    <row r="3" ht="21.0" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="6">
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" ht="21.0" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="7">
         <v>9.0</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-    </row>
-    <row r="4" ht="59.25" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="O4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+    </row>
+    <row r="5" ht="21.75" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-    </row>
-    <row r="6" ht="26.25" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5" t="s">
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" ht="59.25" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-    </row>
-    <row r="7" ht="31.5" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
+      <c r="H6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5" t="s">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-    </row>
-    <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
+      <c r="G7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+    </row>
+    <row r="8" ht="26.25" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="6" t="s">
+      <c r="G8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-    </row>
-    <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="H8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="s">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="5" t="s">
+      <c r="G9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5" t="s">
+      <c r="H9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-    </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="5" t="s">
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5" t="s">
+      <c r="G10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-    </row>
-    <row r="11" ht="38.25" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="H10" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="5" t="s">
+      <c r="I10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="5" t="s">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+    </row>
+    <row r="11" ht="41.25" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3" t="s">
+      <c r="B11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-    </row>
-    <row r="12" ht="96.75" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
+      <c r="G11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="K11" s="8"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="5" t="s">
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-    </row>
-    <row r="13" ht="51.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G12" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="H12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="5" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5" t="s">
+      <c r="N12" s="6"/>
+      <c r="O12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+    </row>
+    <row r="13" ht="38.25" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14" ht="49.5" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="G13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5" t="s">
+      <c r="H13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5" t="s">
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+    </row>
+    <row r="14" ht="96.75" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="G14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
-    </row>
-    <row r="15" ht="123.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="H14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+    </row>
+    <row r="15" ht="51.75" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="G15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5" t="s">
+      <c r="H15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5" t="s">
+      <c r="N15" s="8"/>
+      <c r="O15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-    </row>
-    <row r="16" ht="45.75" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+    </row>
+    <row r="16" ht="49.5" customHeight="1">
+      <c r="A16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
+      <c r="B16" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="C16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="5" t="s">
+      <c r="G16" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="5" t="s">
+      <c r="H16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5" t="s">
+      <c r="L16" s="8"/>
+      <c r="M16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
-    </row>
-    <row r="17" ht="105.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+    </row>
+    <row r="17" ht="123.75" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-    </row>
-    <row r="18" ht="105.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
+      <c r="O17" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+    </row>
+    <row r="18" ht="45.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
     </row>
     <row r="19" ht="105.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
     </row>
     <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
     </row>
     <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
     </row>
     <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
     </row>
     <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
     </row>
     <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
     </row>
     <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
     </row>
     <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
+    </row>
+    <row r="30" ht="105.75" customHeight="1">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+    </row>
+    <row r="31" ht="105.75" customHeight="1">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+    </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2775,7 +2930,12 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,40 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Подкатегория - Основная категория насоса(например: Вихревые насосы серии QB),
-Небольшое описание - например для чего нужен и так далее( в макете под названием на странице насоса),
-Категория - Основная категория насосов(например: Поверхностные (Садовые) насосы),
-Основное фото - Тут указываем название фотографии с расширением(обязательно).например nasos.jpg, nasos.png, 1.webp, 1.png и так далее,
-Дополнительные фотографии -  Тут через запятую указываем фотографии через запятую если их должно быть больше 1 на странице. например(nasos.jpg, nasos.png, 1.webp, 1.png),
-Модель,мощность, подача и так далее -  </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Очень важно, указываем перечиление моделей через запятую. как я показал в примере. В каком порядке указали модель в таком же порядке указываем и все остальные характеристики.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">Тут указываем характеристики насоса, если какой то характеритики нет, ничего в ячейку не ставим, если какой то характеристики не хватает, то добавляем название в столбец и заполняем.
-</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
   <si>
     <t>Категория</t>
   </si>
@@ -398,11 +365,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -410,6 +372,11 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -447,40 +414,37 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -715,814 +679,837 @@
     <col customWidth="1" min="16" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="110.25" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+    </row>
+    <row r="2" ht="21.0" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="6" t="s">
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="8">
+        <v>9.0</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-    </row>
-    <row r="4" ht="21.0" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" ht="59.25" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
-    </row>
-    <row r="6" ht="59.25" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8" t="s">
+      <c r="N5" s="7"/>
+      <c r="O5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+    </row>
+    <row r="6" ht="42.0" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8" t="s">
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+    </row>
+    <row r="7" ht="26.25" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-    </row>
-    <row r="8" ht="26.25" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8" t="s">
+      <c r="N7" s="7"/>
+      <c r="O7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8" t="s">
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8" t="s">
+      <c r="N8" s="7"/>
+      <c r="O8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+    </row>
+    <row r="9" ht="39.75" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
       <c r="O9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+    </row>
+    <row r="10" ht="41.25" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+    </row>
+    <row r="11" ht="42.0" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+    </row>
+    <row r="12" ht="38.25" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" ht="96.75" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="9" t="s">
+      <c r="I13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+    </row>
+    <row r="14" ht="51.75" customHeight="1">
+      <c r="A14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-    </row>
-    <row r="11" ht="41.25" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-    </row>
-    <row r="13" ht="38.25" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-    </row>
-    <row r="14" ht="96.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-    </row>
-    <row r="15" ht="51.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="C14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="8" t="s">
+      <c r="N14" s="7"/>
+      <c r="O14" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8" t="s">
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+    </row>
+    <row r="15" ht="49.5" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-    </row>
-    <row r="16" ht="49.5" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
+      <c r="L15" s="7"/>
+      <c r="M15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8" t="s">
+      <c r="N15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="O15" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+    </row>
+    <row r="16" ht="123.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-    </row>
-    <row r="17" ht="123.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
+      <c r="L16" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8" t="s">
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+    </row>
+    <row r="17" ht="45.75" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
-    </row>
-    <row r="18" ht="45.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="C17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+    </row>
+    <row r="18" ht="105.75" customHeight="1">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
     </row>
     <row r="19" ht="105.75" customHeight="1">
       <c r="A19" s="11"/>
@@ -1539,435 +1526,408 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
     </row>
     <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
     </row>
     <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
     </row>
     <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
     </row>
     <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
     </row>
     <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
     </row>
     <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
     </row>
     <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
     </row>
     <row r="30" ht="105.75" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-    </row>
-    <row r="31" ht="105.75" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-    </row>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2931,11 +2891,7 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
-  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,7 +11,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Подкатегория - Основная категория насоса(например: Вихревые насосы серии QB),
+Небольшое описание - например для чего нужен и так далее( в макете под названием на странице насоса),
+Категория - Основная категория насосов(например: Поверхностные (Садовые) насосы),
+Основное фото - Тут указываем название фотографии с расширением(обязательно).например nasos.jpg, nasos.png, 1.webp, 1.png и так далее,
+Дополнительные фотографии -  Тут через запятую указываем фотографии через запятую если их должно быть больше 1 на странице. например(nasos.jpg, nasos.png, 1.webp, 1.png),
+Модель,мощность, подача и так далее -  </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Очень важно, указываем перечиление моделей через запятую. как я показал в примере. В каком порядке указали модель в таком же порядке указываем и все остальные характеристики.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Тут указываем характеристики насоса, если какой то характеритики нет, ничего в ячейку не ставим, если какой то характеристики не хватает, то добавляем название в столбец и заполняем.
+</t>
+    </r>
+  </si>
   <si>
     <t>Категория</t>
   </si>
@@ -365,6 +398,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -372,11 +410,6 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -414,37 +447,40 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,837 +715,814 @@
     <col customWidth="1" min="16" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="110.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+    <row r="3" ht="21.0" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="5" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" ht="21.0" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-    </row>
-    <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+    </row>
+    <row r="5" ht="21.75" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
+      <c r="H5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="6">
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="9">
         <v>9.0</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-    </row>
-    <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="8">
-        <v>9.0</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-    </row>
-    <row r="5" ht="59.25" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="O5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" ht="59.25" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7" t="s">
+      <c r="H6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-    </row>
-    <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7" t="s">
+      <c r="H7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-    </row>
-    <row r="7" ht="26.25" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7" t="s">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+    </row>
+    <row r="8" ht="26.25" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7" t="s">
+      <c r="H8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7" t="s">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7" t="s">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7" t="s">
+      <c r="H9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7" t="s">
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-    </row>
-    <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7" t="s">
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="C10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="8" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-    </row>
-    <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+    </row>
+    <row r="11" ht="41.25" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="C11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="7" t="s">
+      <c r="H11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7" t="s">
+      <c r="K11" s="8"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="7" t="s">
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7" t="s">
+      <c r="H12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-    </row>
-    <row r="12" ht="38.25" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7" t="s">
+      <c r="N12" s="6"/>
+      <c r="O12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+    </row>
+    <row r="13" ht="38.25" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="C13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="7" t="s">
+      <c r="H13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-    </row>
-    <row r="13" ht="96.75" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7" t="s">
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+    </row>
+    <row r="14" ht="96.75" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7" t="s">
+      <c r="H14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-    </row>
-    <row r="14" ht="51.75" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+    </row>
+    <row r="15" ht="51.75" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="7" t="s">
+      <c r="H15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15" ht="49.5" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="N15" s="8"/>
+      <c r="O15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+    </row>
+    <row r="16" ht="49.5" customHeight="1">
+      <c r="A16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="C16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7" t="s">
+      <c r="H16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="L16" s="8"/>
+      <c r="M16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="N16" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-    </row>
-    <row r="16" ht="123.75" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="O16" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7" t="s">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+    </row>
+    <row r="17" ht="123.75" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="C17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7" t="s">
+      <c r="L17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-    </row>
-    <row r="17" ht="45.75" customHeight="1">
-      <c r="A17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7" t="s">
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+    </row>
+    <row r="18" ht="45.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="H18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7" t="s">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-    </row>
-    <row r="18" ht="105.75" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
     </row>
     <row r="19" ht="105.75" customHeight="1">
       <c r="A19" s="11"/>
@@ -1526,408 +1539,435 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
     </row>
     <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
     </row>
     <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-      <c r="Z21" s="11"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
     </row>
     <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
     </row>
     <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11"/>
-      <c r="Z23" s="11"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
     </row>
     <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-      <c r="Z24" s="11"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
     </row>
     <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
     </row>
     <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-      <c r="Z26" s="11"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="11"/>
-      <c r="Z27" s="11"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="11"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
-      <c r="Z29" s="11"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
     </row>
     <row r="30" ht="105.75" customHeight="1">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+    </row>
+    <row r="31" ht="105.75" customHeight="1">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+    </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -2891,7 +2931,11 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="115">
   <si>
     <r>
       <rPr>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Модель</t>
+  </si>
+  <si>
+    <t>Фотографии моделей</t>
   </si>
   <si>
     <t>Мощность, кВт</t>
@@ -447,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -455,12 +458,18 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
@@ -697,22 +706,23 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="33.5"/>
+    <col customWidth="1" min="1" max="1" width="40.75"/>
     <col customWidth="1" min="2" max="2" width="29.88"/>
-    <col customWidth="1" min="3" max="3" width="14.0"/>
+    <col customWidth="1" min="3" max="3" width="31.25"/>
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="35.63"/>
     <col customWidth="1" min="6" max="6" width="40.88"/>
-    <col customWidth="1" min="7" max="7" width="18.88"/>
-    <col customWidth="1" min="8" max="8" width="19.13"/>
-    <col customWidth="1" min="9" max="9" width="31.63"/>
-    <col customWidth="1" min="10" max="10" width="30.75"/>
-    <col customWidth="1" min="11" max="11" width="31.13"/>
-    <col customWidth="1" min="12" max="12" width="14.38"/>
-    <col customWidth="1" min="13" max="13" width="22.88"/>
-    <col customWidth="1" min="14" max="14" width="35.0"/>
-    <col customWidth="1" min="15" max="15" width="32.63"/>
-    <col customWidth="1" min="16" max="26" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="32.63"/>
+    <col customWidth="1" min="8" max="8" width="18.88"/>
+    <col customWidth="1" min="9" max="9" width="19.13"/>
+    <col customWidth="1" min="10" max="10" width="31.63"/>
+    <col customWidth="1" min="11" max="11" width="30.75"/>
+    <col customWidth="1" min="12" max="12" width="31.13"/>
+    <col customWidth="1" min="13" max="13" width="14.38"/>
+    <col customWidth="1" min="14" max="14" width="22.88"/>
+    <col customWidth="1" min="15" max="15" width="35.0"/>
+    <col customWidth="1" min="16" max="16" width="32.63"/>
+    <col customWidth="1" min="17" max="27" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="110.25" customHeight="1">
@@ -739,7 +749,7 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -766,1207 +776,1246 @@
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-    </row>
-    <row r="3" ht="21.0" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="6" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+    </row>
+    <row r="4" ht="36.0" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-    </row>
-    <row r="4" ht="21.0" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
+    </row>
+    <row r="5" ht="39.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
+      <c r="I5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="7">
+      <c r="M5" s="10"/>
+      <c r="N5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="11">
         <v>9.0</v>
       </c>
-      <c r="O4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
+      <c r="P5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
     </row>
     <row r="6" ht="59.25" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
+      <c r="I6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="O6" s="10"/>
+      <c r="P6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8" t="s">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+    </row>
+    <row r="7" ht="48.0" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8" t="s">
+      <c r="I7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
     </row>
     <row r="8" ht="26.25" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8" t="s">
+      <c r="A8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8" t="s">
+      <c r="I8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8" t="s">
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
     </row>
     <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
+      <c r="A9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8" t="s">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8" t="s">
+      <c r="I9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8" t="s">
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
+      <c r="A10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8" t="s">
+      <c r="J10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="9" t="s">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
     </row>
     <row r="11" ht="41.25" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="8"/>
+      <c r="I11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="L11" s="10"/>
-      <c r="M11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8" t="s">
+      <c r="M11" s="12"/>
+      <c r="N11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
     </row>
     <row r="13" ht="38.25" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8" t="s">
+      <c r="A13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="C13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="8" t="s">
+      <c r="I13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6" t="s">
+      <c r="L13" s="9"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+      <c r="AA13" s="12"/>
     </row>
     <row r="14" ht="96.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="A14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="8" t="s">
+      <c r="I14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14" s="10"/>
       <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
+      <c r="AA14" s="12"/>
     </row>
     <row r="15" ht="51.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="A15" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="I15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8" t="s">
+      <c r="M15" s="12"/>
+      <c r="N15" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
     </row>
     <row r="16" ht="49.5" customHeight="1">
-      <c r="A16" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="B16" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8" t="s">
+      <c r="I16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="M16" s="10"/>
+      <c r="N16" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O16" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
+      <c r="P16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
     </row>
     <row r="17" ht="123.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="A17" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="C17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
+      <c r="J17" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="K17" s="10"/>
+      <c r="L17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8" t="s">
+      <c r="M17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
     </row>
     <row r="18" ht="45.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
+      <c r="A18" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="C18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="I18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8" t="s">
+      <c r="K18" s="10"/>
+      <c r="L18" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
     </row>
     <row r="19" ht="105.75" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
     </row>
     <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
     </row>
     <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
     </row>
     <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
     </row>
     <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
     </row>
     <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
     </row>
     <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
     </row>
     <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
     </row>
     <row r="30" ht="105.75" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
     </row>
     <row r="31" ht="105.75" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
@@ -2934,7 +2983,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="227">
   <si>
     <r>
       <rPr>
@@ -64,9 +64,6 @@
     <t>Модель</t>
   </si>
   <si>
-    <t>Фотографии моделей</t>
-  </si>
-  <si>
     <t>Мощность, кВт</t>
   </si>
   <si>
@@ -94,16 +91,15 @@
     <t>Присоединительный размер (дюйм)</t>
   </si>
   <si>
+    <t>Монтажная длина (мм)</t>
+  </si>
+  <si>
     <t>Поверхностные (Садовые) насосы</t>
   </si>
   <si>
     <t>Насосы серии QB</t>
   </si>
   <si>
-    <t>Вихревые насосы серии QB предназначены для подачи чистой воды без абразивных примесей. 
-Они обеспечивают надежную и стабильную работу в бытовых и хозяйственных системах водоснабжения, где требуется чистая вода без твердых включений.</t>
-  </si>
-  <si>
     <t>nasos.jpg</t>
   </si>
   <si>
@@ -236,10 +232,10 @@
     <t>2"</t>
   </si>
   <si>
-    <t>Насос скважинный</t>
-  </si>
-  <si>
-    <t>Вентовые  3"</t>
+    <t>Скважинные насосы</t>
+  </si>
+  <si>
+    <t>Насосы серии QJD (винтовые)</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI 3QGD1-30-0.25, ENSI 3QGD1-45-0.37, ENSI 3QGD1.2-60-0.55                              </t>
@@ -257,7 +253,7 @@
     <t>1"</t>
   </si>
   <si>
-    <t>Однофазные  3"</t>
+    <t>Насосы серии TF3 (диаметр  75мм)</t>
   </si>
   <si>
     <t xml:space="preserve">ENSI  TF3-1/30, ENSI  TF3-1/40, ENSI  TF3-1/60, ENSI  TF3-1/80, ENSI  TF3-1/110, ENSI  TF3-1/140, ENSI  TF3-1/180      </t>
@@ -272,7 +268,7 @@
     <t xml:space="preserve">33 , 46 , 65 , 90 , 123 , 123 164 , 205  </t>
   </si>
   <si>
-    <t>Однофазные 4"</t>
+    <t>Насосы серии TF3 (диаметр  98мм)</t>
   </si>
   <si>
     <t>ENSI TF4-3/60,  ENSI TF4-3/80, ENSI TF4-3/120, ENSI TF4-3/140,  ENSI TF4-3/160, ENSI TF4-3/190, ENSI TF4-3/220</t>
@@ -290,7 +286,7 @@
     <t>1¼"</t>
   </si>
   <si>
-    <t>Трехфазные 4"</t>
+    <t>Насосы серии SP (корпус и рабочие колеса из нержавеющей стали)</t>
   </si>
   <si>
     <t>ENSI 4SР3-15, ENSI 4SР3-18,  ENSI 4SР3-22,  ENSI 4SР3-25,  ENSI 4SР3-29,  ENSI 4SР5-15, ENSI 4SР5-17, ENSI 4SР5-21, ENSI 4SР5-25, ENSI 4SР5-29, ENSI 4SР5-33, ENSI 4SР8-15, ENSI 4SР8-18, ENSI 4SР8-21, ENSI 4SР8-25, ENSI 4SР8-30, ENSI 4SР8-36,  ENSI 4SР14-13,  ENSI 4SР14-16,  ENSI 4SР14-18, ENSI 4SР14-21,  ENSI 4SР14-24</t>
@@ -305,7 +301,10 @@
     <t>94, 113, 138, 157, 182, 95, 108, 134, 159, 185, 210, 95, 114, 133, 159, 191, 229, 89, 110, 124, 144, 165</t>
   </si>
   <si>
-    <t>Трехфазные 5-6"</t>
+    <t>1¼", 1¼", 1¼", 1¼", 1¼", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2", 2"</t>
+  </si>
+  <si>
+    <t>Насосы серии SR (корпус нержавеющая сталь, рабочие колеса полимер)</t>
   </si>
   <si>
     <t>ENSI 5SR10/13, ENSI 5SR10/16, ENSI 6SR10/08, ENSI 6SR10/11, ENSI 6SR10/14, ENSI 6SR10/14, ENSI 6SR10/20, ENSI 6SR18/10, ENSI 6SR18/15, ENSI 6SR30/11</t>
@@ -323,6 +322,177 @@
     <t>3"</t>
   </si>
   <si>
+    <t>Циркуляционные насосы с "мокрым" ротором</t>
+  </si>
+  <si>
+    <t>Насосы серии GPD</t>
+  </si>
+  <si>
+    <t>ENSI GPD 20-4S, ENSI GPD 20-6S, ENSI GPD 25-4S-180, ENSI GPD 25-6S-180, ENSI GPD 25-4S-130, ENSI GPD 25-6S-130, ENSI GPD 25-8S, ENSI GPD 32-4S-180, ENSI GPD 32-6S-180, ENSI GPD 32-8S</t>
+  </si>
+  <si>
+    <t>0.032/0.050/0.065, 0.055/0.070/0.10, 0.032/0.050/0.065, 0.055/0.070/0.10, 0.032/0.050/0.065, 0.055/0.070/0.10, 0.135/0.190/0.245, 0.032/0.050/0.065, 0.055/0.070/0.10, 0.135/0.190/0.245</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.9, 2.9, 3.2, 3.2,  3.2, 3.2, 10.2,  3.5, 3.5, 10.2  </t>
+  </si>
+  <si>
+    <t>9, 4, 6, 4, 6, 4, 6, 8, 4, 6, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3/4", 3/4", 1", 1", 1", 1", 1", 11/4", 11/4", 11/4"</t>
+  </si>
+  <si>
+    <t>160, 130, 130, 180, 180, 130, 130, 180, 180, 180, 180</t>
+  </si>
+  <si>
+    <t>Насосы серии  LRS</t>
+  </si>
+  <si>
+    <t>ENSI LRS 20/4-130G, ENSI LRS 20/6-130G, ENSI  LRS 25/12-180G, ENSI  LRS 25/4-130G, ENSI  LRS 25/4-180G, ENSI LRS 25/6-130G, ENSI LRS 25/6-180G, ENSI LRS 25/8-180G, ENSI LRS 32/4-130, ENSI LRS 32/4-180G, ENSI  LRS 32/6-130, ENSI LRS 32/6-180G, ENSI LRS 32/8-180G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038/0.053/0.072, 0.046/0.067/0.093, 0.15/0.20/0.27, 0.038/0.053/0.072, 0.038/0.053/0.072, 0.046/0.067/0.093,0.046/0.067/0.093, 0.15/0.20/0.27, 0.038/0.053/0.072, 0.038/0.053/0.072, 0.046/0.067/0.093,0.046/0.067/0.093, 0.15/0.20/0.27  </t>
+  </si>
+  <si>
+    <t>2.5, 2.8, 4, 2.8, 2.8, 3.3, 3.3, 9, 2.8, 2.8, 3.3, 3.3, 9.6</t>
+  </si>
+  <si>
+    <t>9, 4, 6, 12, 4, 4, 6, 6, 8, 4, 4, 6, 6, 8</t>
+  </si>
+  <si>
+    <t>3/4", 3/4", 1", 1", 1", 1", 1", 1", 11/4", 11/4", 11/4", 11/4", 11/4"</t>
+  </si>
+  <si>
+    <t>Насосы серии  LPS</t>
+  </si>
+  <si>
+    <t>ENSI LPS 25-4-130 BPE1, ENSI LPS 25-6-130 BPE1, ENSI LPS 25-8-130 BPE1, ENSI LPS 25-8-180 BPE1, ENSI LPS 32-8-180 BPE1, ENSI LPS PC 25-12-180, ENSI LPS PC 32-12-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.022, 0.045, 0.060, 0.060, 0.060, 0.22, 0.22</t>
+  </si>
+  <si>
+    <t>46, 52, 60, 60, 70, 125, 160</t>
+  </si>
+  <si>
+    <t>4, 6, 8, 8, 8,12,12</t>
+  </si>
+  <si>
+    <t>1", 1", 1", 1, 11/4", 1", 11/4"</t>
+  </si>
+  <si>
+    <t>130, 130, 130, 180, 180, 180, 180</t>
+  </si>
+  <si>
+    <t>Насосы серии  GPD (Фланцы)</t>
+  </si>
+  <si>
+    <t>ENSI GPD 40-12F/250, ENSI GPD 40-16F/250, ENSI GPD 50-12F/280, ENSI GPD 65-12F/300</t>
+  </si>
+  <si>
+    <t>0.70, 1, 1, 1.3</t>
+  </si>
+  <si>
+    <t>13, 15, 26, 45</t>
+  </si>
+  <si>
+    <t>12, 16, 12, 12</t>
+  </si>
+  <si>
+    <t>40, 40, 50, 65</t>
+  </si>
+  <si>
+    <t>250, 250 ,280, 300</t>
+  </si>
+  <si>
+    <t>Насосы серии  GPS (Фланцы)</t>
+  </si>
+  <si>
+    <t>ENSI GPS 40-12SF/250, ENSI GPS 40-16SF/250, ENSI GPS 50-12SF/280, ENSI GPS 50-16SF/280, ENSI GPS 50-20SF/280, ENSI GPS 65-12SF/300, ENSI GPS 80-10SF/360, ENSI GPS 80-12SF/360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40/0.45/0.70, 0.60/0.70/1, 0.60/0.70/1, 0.9/1/1.3, 0.9/1/1.3, 0.9/1/1.3, 0.60/0.70/1, 0.9/1/1.3,   </t>
+  </si>
+  <si>
+    <t>14, 16, 25, 32, 24, 50, 35, 48</t>
+  </si>
+  <si>
+    <t>12, 16, 12, 16, 20, 12, 10,12</t>
+  </si>
+  <si>
+    <t>40, 40, 50, 50, 50, 65, 80, 80</t>
+  </si>
+  <si>
+    <t>250, 250, 280, 280, 280,300, 360, 360</t>
+  </si>
+  <si>
+    <t>Серия GRSF (Фланцы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENSI GRSF40-13S-250, ENSI GRSF40-18S-250, ENSI GRSF50-13S-280, ENSI GRSF50-18S-280, ENSI GRSF65-18S-340, ENSI GRSF65-9S-340 </t>
+  </si>
+  <si>
+    <t>0.69/0.73/0.8, 0.77/0.89/1.1, 0.79/0.96/1.14, 0.8/0.96/1.36, 1.06/1.23/1.725, 0.74/0.85/1.06</t>
+  </si>
+  <si>
+    <t>220В 50Гц, 220В 50Гц, 220В 50Гц, 220В 50Гц,  380В 50Гц, 220В 50Гц</t>
+  </si>
+  <si>
+    <t>15.8, 16.2, 24.9, 28.2, 44.3, 36</t>
+  </si>
+  <si>
+    <t>12.8, 17.2, 13, 17.4, 18, 10</t>
+  </si>
+  <si>
+    <t>40, 40, 50, 50, 65, 65</t>
+  </si>
+  <si>
+    <t>250, 250, 280, 280, 340, 340</t>
+  </si>
+  <si>
+    <t>Серия LRSF  (Фланцы)</t>
+  </si>
+  <si>
+    <t>ENSI LRSF 32-120 220, ENSI LRSF 40-120 250, ENSI  LRSF 40-160 250, ENSI LRSF 40-80-200, ENSI LRSF 50-120-280, ENSI  LRSF 50-160 280</t>
+  </si>
+  <si>
+    <t>0.55, 0.7, 1, 0.14/0.21/0.26, 1, 1.3</t>
+  </si>
+  <si>
+    <t>11, 15, 15, 8.1, 27, 27</t>
+  </si>
+  <si>
+    <t>13, 16, 19, 8, 14, 18</t>
+  </si>
+  <si>
+    <t>32, 40, 40, 40, 50, 50</t>
+  </si>
+  <si>
+    <t>220, 250, 250, 200, 280, 280</t>
+  </si>
+  <si>
+    <t>Насосы серии  MEGA (Фланцы)</t>
+  </si>
+  <si>
+    <t>ENSI Mega 40-10F, ENSI Mega S 50-18F, ENSI Mega S 65-12F</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0,010/0.185, 0.035/0.75, 0.035/0.75</t>
+  </si>
+  <si>
+    <t>11, 32, 35</t>
+  </si>
+  <si>
+    <t>10, 18, 12</t>
+  </si>
+  <si>
+    <t>40, 50, 65</t>
+  </si>
+  <si>
+    <t>220, 280, 340</t>
+  </si>
+  <si>
     <t>Горизонтальные многоступенчатые насосы</t>
   </si>
   <si>
@@ -387,6 +557,171 @@
   </si>
   <si>
     <t>1" × 1", 1" × 1", 1" × 1"</t>
+  </si>
+  <si>
+    <t>Канализационные установки</t>
+  </si>
+  <si>
+    <t>Насосы серии  MP (Профи)</t>
+  </si>
+  <si>
+    <t>Насосы серии MP-F (Эконом)</t>
+  </si>
+  <si>
+    <t>Насосы серии HIMPOO (Пром)</t>
+  </si>
+  <si>
+    <t>Жироуловители</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Насосы "In-Line" ( в линию) </t>
+  </si>
+  <si>
+    <t>Насосы серии PT</t>
+  </si>
+  <si>
+    <t>ENSI РТ100-270/110, ENSI РТ100-320/150, ENSI РТ100-390/185, ENSI РТ100-600/300, ENSI РТ50-170/7, ENSI РТ50-410/40, ENSI РТ50-460/55, ENSI РТ65-320/55, ENSI РТ65-380/40, ENSI РТ65-400/75, ENSI РТ80-190/40, ENSI РТ80-230/55, ENSI РТ80-270/75, ENSI РТ80-330/92, ENSI РТ80-360/110, ENSI РТ80-420/150</t>
+  </si>
+  <si>
+    <t>11, 15, 18.5, 30, 0.75, 4, 5.5, 5.5, 4, 7.5, 4, 5.5, 7.5, 9.2, 11, 15</t>
+  </si>
+  <si>
+    <t>180, 210, 210, 210, 18, 42, 48, 84, 42, 90, 108, 108, 120, 120, 120, 138</t>
+  </si>
+  <si>
+    <t>27, 32, 39, 60, 17.5, 41, 46, 32, 25, 40, 19, 23, 27, 33, 36, 42</t>
+  </si>
+  <si>
+    <t>552, 552, 552, 552, 340, 440, 440, 400, 400, 400, 470, 470, 470, 470, 470, 470</t>
+  </si>
+  <si>
+    <t>Насосы серии PTD</t>
+  </si>
+  <si>
+    <t>ENSI PTD 100-15/2, ENSI PTD 100-17/2, ENSI PTD 100-17/G2, ENSI PTD 100-22/2, ENSI PTD 100-33/2, ENSI PTD 100-40/2, ENSI PTD 100-48/2, ENSI PTD 100-52/2, ENSI PTD 100-52/G2, ENSI PTD 100-9/2, ENSI PTD 125-11/4, ENSI PTD 125-14/4, ENSI PTD 125-18/4, ENSI PTD 125-20/4, ENSI PTD 125-22/4, ENSI PTD 125-28/4, ENSI PTD 125-32/4, ENSI PTD 32-18/G2, ENSI PTD 32-25/2, ENSI PTD 32-33/G2, ENSI PTD 32-38/2, ENSI PTD 40-16/2, ENSI PTD 40-16/G2, ENSI PTD 40-18/2, ENSI PTD 40-20/G2, ENSI PTD 40-21/G2, ENSI PTD 40-26/G2, ENSI PTD 40-30/G2, ENSI PTD 50-15/G2, ENSI PTD 50-18/G2, ENSI PTD 50-24/G2, ENSI PTD 50-28/G2, ENSI PTD 50-35/G2, ENSI PTD 50-50/2, ENSI PTD 65-20/G2, ENSI PTD 65-22/G2, ENSI PTD 65-30/2, ENSI PTD 65-30/G2, ENSI PTD 65-34/G2, ENSI PTD 65-37/G2, ENSI PTD 65-40G/2, ENSI PTD 80-18/G2, ENSI PTD 80-23/G2, ENSI PTD 80-29/G2, ENSI PTD 80-32/G2, ENSI PTD 80-38/2, ENSI PTD 80-54/2</t>
+  </si>
+  <si>
+    <t>4, 5.5, 5.5, 7.5, 15, 18.5, 22, 30, 30, 2.2, 5.5, 7.5, 11, 11, 15, 18.5, 22, 1.1, 2.2, 3, 4, 1.1, 1.1, 2.2, 2.2, 1.5, 3, 4, 1.5, 2.2, 3, 4, 5.5, 11, 2.2, 3, 4, 5.5, 5.5, 7.5, 5.5, 11, 4, 5.5, 7.5, 11, 15, 22</t>
+  </si>
+  <si>
+    <t>60, 80, 80, 80, 100, 100, 100, 130, 130, 50, 120, 120, 160, 120, 160, 160, 160, 8, 12.5, 12.5, 12.5, 12.5, 12.5, 20, 20, 12.5, 20, 25, 20, 20, 25, 30, 30, 40, 30, 30, 40, 40, 40, 50, 25, 50, 50, 50, 50, 70, 80, 80</t>
+  </si>
+  <si>
+    <t>15, 17, 17, 22, 33, 40, 48, 52, 52, 9, 11, 14, 18, 20, 22, 28, 32, 18, 25, 33, 38, 16, 16, 18, 20, 21, 26, 30, 15, 18, 24, 28, 35, 50, 15, 20, 22, 30, 30, 34, 37, 40, 18, 23, 29, 32, 38, 54</t>
+  </si>
+  <si>
+    <t>450, 500, 500, 500, 550, 550, 550, 550, 550, 450, 620, 620, 660, 800, 800, 800, 800, 320, 320, 340, 360, 320, 320, 320, 320, 320, 340, 340, 340, 340, 340, 340, 340, 440, 340, 340, 340, 360, 360, 360, 400, 400, 400, 400, 400, 450, 500, 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Консольно-моноблочные насосы </t>
+  </si>
+  <si>
+    <t>Насосы серии PST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-125/11 (DN50x32) ,32-160/22 (DN50x32) , 32-160/30  (DN50x32) , 32-200/30  (DN50x32) , 32-200/40  (DN50x32) , 32-250/55 (DN50x32) , 40-125/15 (DN65x40), 40-125/22 (DN65x40) , 40-160/30 (DN65x40), 40-160/40 (DN65x40) , 40-200/55 (DN65x40) , 40-200/75 (DN65x40) ,40-250/110 (DN65x40) , 40-250/92(DN65x40), 50-125/30 (DN65x50), 50-125/40 (DN65x50) , 50-160/55 (DN65x50) , 50-160/75 (DN65x50) 50-200/110 (DN65x50), 50-200/150 (DN65x50) ,50-200/92 (DN65x50) , 50-250/150 (DN65x50) , 65-125/55 (DN80x65) , 65-125/75 (DN80x65), 65-160/110 (DN80x65) , 65-160/150 (DN80x65) , 65-160/92 (DN80x65) , 65-200/150 (DN80x65) , 65-200/185 (DN80x65) , 65-200/220 (DN80x65) ,65-250/220 (DN80x65) , 80-110/220 (DN100x80) , 80-125/75 (DN100x80) , 80-160/110 (DN100x80) , 80-160/150 (DN100x80) , 80-160/185 (DN100x80) ,80-160/220 (DN100x80) , Насос ENSI PST80-200/220 (DN100x80),80-200/300 (DN100x80) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 , 3, 4, 5.5 , 2.2 , 3 ,4 ,5.5,7.5,9.2 , 3, 4, 5.5 , 11 , 9.2 ,15, 5.5 ,11 , 15 , 15 ,18.5 , 22 , 22 , 7.5 , 11 , 15 , 18.5 , 22 , 30 </t>
+  </si>
+  <si>
+    <t>24 ,27,27,27,48,48,48,45,48,48,72,84,84,90,84,90,120,138,138,138,180,210,210,210,210,210,</t>
+  </si>
+  <si>
+    <t>22, 44 ,54,5 , 60, 24,5 31,8 ,38,46,57,64,20,24,32,55,50,5,68.5,23,35,42,45,52,59,64,8,26,28,32.8,39,44,60</t>
+  </si>
+  <si>
+    <t>Вертикальные многоступенчатые насосы</t>
+  </si>
+  <si>
+    <t>Насосы серии CDL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 СDL2-110 ВР, 25 СDL2-150, 25 СDL2-180 , 25 СDL3-210 , 25 СDL3-230, 25 СDLF2-110 ВР ,25 СDLF2-130 ,25 СDLF2-150 , 25 СDLF2-150 ВР , 25 СDLF2-180 , 25 СDLF2-180 ВР , 25 СDLF2-220 , 25 СDLF3-230 , 25 СDLF3-250 , 25 СDLF3-290 ,32 CDL4-100 , 32 CDL4-120 ,32 CDL4-140 , 32 CDL4-160 , 32 CDL4-30 , 32 CDL4-40 , 32 CDL4-50, 32 CDL4-60 ,32 CDL4-70 , 32 CDL4-80 ,32 СDLF4-100 , 32 СDLF4-120 ,32 СDLF4-140 , 32 СDLF4-160 , 32 СDLF4-30 , 32 СDLF4-40 , 32 СDLF4-60 ,32 СDLF4-70 , 40 CDL8-20 , 40 CDL8-30 , 40 CDL8-40 , 40 CDL8-50 , 40 CDL8-60 , 40 CDL8-80 , 40 СDL8-120, 40 СDLF8-100 , 40 СDLF8-120 ,40 СDLF8-20 , 40 СDLF8-30, 40 СDLF8-40 , 40 СDLF8-50 , 40 СDLF8-60 ,40 СDLF8-80 , 50 CDL12-20 ,50 CDL12-30 , 50 CDL12-40 , 50 CDL12-50 , 50 СDL12-60 , 50 СDL16-30 , 50 СDL16-40 , 50 СDL16-50 , 50 СDL16-60 , 50 СDL20-30 , 50 СDL20-40 , 50 СDL20-50 , 50 СDLF12-20 , 50 СDLF12-30 , 50 СDLF12-40 , 50 СDLF12-50 , 50 СDLF12-60 , 50 СDLF16-20 , 50 СDLF16-40 , 50 СDLF16-50 , 50 СDLF20-170 , 50 СDLF20-30 , 65 СDL32-30 , 65 СDL32-40 , 65 СDL32-50 , 65 СDL32-60 , 80 СDL45-20 , 80 СDL45-30 , 80 СDL45-40  100 СDL90-30-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 , 1.5 ,2.2 , 2.2, 2.2, 2.2, 2.2, 2.2 , 2.2, 2.2, 3, 3, 0.55 , 0.75 ,1.1 , 1.1, 1.5 , 1.5, 0.75, 1.1, 1.1, 1.5, 1.5, 0.75, 1.1, 1.1, 1.5, 2.2, 2.2, 3, 4, 4, 1.5 2.2, 3, 3, 4, 3, 1, 2.2 2.2, 4, 5.5, 4, 5.5, 7.5, 11, 7.5, 11, 15, 18.5 </t>
+  </si>
+  <si>
+    <t>3.5, 3.5, 3.5, 4, 4, 3,5 , 4, 8, 8, 8, 8, 8, 8, 8, 8, 8, 8, 12, 12, 12, 12, 12, 12, 12, 12,  16, 16, 16, 16, 16, 22, 22, 22, 22, 28, 40, 40, 40, 55, 55, 55, 110</t>
+  </si>
+  <si>
+    <t>82, 112 , 136, 98, 107, 136, 116, 81, 95, 112, 129, 24 , 32, 40 , 48, 56, 64, 18, 26 , 35, 44, 53 , 72, 111, 92, 20 , 30, 40, 50, 60, 34, 46, 60 69, 35,10 ,53 ,67 ,39 ,58 ,78</t>
+  </si>
+  <si>
+    <t>98, 134, 161, 128, 140, 161, 151, 96, 114, 136, 152, 32, 38, 47, 56, 66, 74, 20, 30, 41, 52, 62, 83, 124, 104, 23, ,2, 47, 59, 71, 41, 54, 72, 83, 40 , 54, 72, 90, 48, 71, 95, 68</t>
+  </si>
+  <si>
+    <t>Опрессовочные "испытательные" насосы</t>
+  </si>
+  <si>
+    <t>Ручные</t>
+  </si>
+  <si>
+    <t>Электрические</t>
+  </si>
+  <si>
+    <t>Насосы и оборудование для ГСМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кран ручной топливораздаточный </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENSI TSN - М1 (вход 1") , ENSI TSN-С1 (вх.1") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Насос бочковой погружной </t>
+  </si>
+  <si>
+    <t>ENSI ТНР-12 (нержавеющая сталь) ,  ENSI ТНР-СН (PP+SS304 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Насос самовсасывающий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSO-R (24V) ДТ , TSO A100 (220V) ДТ, TSM-240 , </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,175 , 0.3 </t>
+  </si>
+  <si>
+    <t>60л/м , 60л/м  , 40л/м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 , 30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Аксессуары  и комплектующие</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   TSM-B.  Алюмин быстроразъём соединение Тип D DN 50 , Алюмин быстроразъём соединение Тип DP DN 75 , Фильтр TSF-300 , Фильтр с прозрачным корпусом TSF-GL-A нерж.</t>
+  </si>
+  <si>
+    <t>Гидроаккумуляторы и расширительные баки</t>
+  </si>
+  <si>
+    <t>Гидроаккумуляторы</t>
+  </si>
+  <si>
+    <t>Расширительные баки</t>
+  </si>
+  <si>
+    <t>Гидроаккумуляторы и расширительные баки из нержавеющей стали</t>
+  </si>
+  <si>
+    <t>Запчасти для гиджроаккумуляторов и расширительных баков</t>
+  </si>
+  <si>
+    <t>Автоматика и управление</t>
+  </si>
+  <si>
+    <t>Аксессуары и комплектующие</t>
+  </si>
+  <si>
+    <t>Ручные насосы</t>
+  </si>
+  <si>
+    <t>Мотопомпы</t>
   </si>
 </sst>
 </file>
@@ -450,7 +785,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -458,18 +793,13 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
@@ -490,7 +820,7 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,31 +1036,31 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.75"/>
+    <col customWidth="1" min="1" max="1" width="33.5"/>
     <col customWidth="1" min="2" max="2" width="29.88"/>
-    <col customWidth="1" min="3" max="3" width="31.25"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="5" width="35.63"/>
-    <col customWidth="1" min="6" max="6" width="40.88"/>
-    <col customWidth="1" min="7" max="7" width="32.63"/>
-    <col customWidth="1" min="8" max="8" width="18.88"/>
-    <col customWidth="1" min="9" max="9" width="19.13"/>
-    <col customWidth="1" min="10" max="10" width="31.63"/>
-    <col customWidth="1" min="11" max="11" width="30.75"/>
-    <col customWidth="1" min="12" max="12" width="31.13"/>
-    <col customWidth="1" min="13" max="13" width="14.38"/>
-    <col customWidth="1" min="14" max="14" width="22.88"/>
-    <col customWidth="1" min="15" max="15" width="35.0"/>
-    <col customWidth="1" min="16" max="16" width="32.63"/>
-    <col customWidth="1" min="17" max="27" width="11.0"/>
+    <col customWidth="1" min="3" max="3" width="21.0"/>
+    <col customWidth="1" min="4" max="4" width="16.0"/>
+    <col customWidth="1" min="5" max="5" width="33.63"/>
+    <col customWidth="1" min="6" max="6" width="41.63"/>
+    <col customWidth="1" min="7" max="7" width="18.88"/>
+    <col customWidth="1" min="8" max="8" width="19.13"/>
+    <col customWidth="1" min="9" max="9" width="31.63"/>
+    <col customWidth="1" min="10" max="10" width="30.75"/>
+    <col customWidth="1" min="11" max="11" width="31.13"/>
+    <col customWidth="1" min="12" max="12" width="14.38"/>
+    <col customWidth="1" min="13" max="13" width="22.88"/>
+    <col customWidth="1" min="14" max="14" width="35.0"/>
+    <col customWidth="1" min="15" max="15" width="32.63"/>
+    <col customWidth="1" min="16" max="16" width="20.63"/>
+    <col customWidth="1" min="17" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="110.25" customHeight="1">
+    <row r="1" ht="75.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="28.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -749,7 +1079,7 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -776,7 +1106,7 @@
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q2" s="4"/>
@@ -789,1294 +1119,3189 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-    </row>
-    <row r="3" ht="29.25" customHeight="1">
+    </row>
+    <row r="3" ht="21.0" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="8">
+        <v>8.0</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="8" t="s">
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+    </row>
+    <row r="4" ht="21.0" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="8">
+        <v>9.0</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="9">
-        <v>8.0</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-    </row>
-    <row r="4" ht="36.0" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" ht="21.75" customHeight="1">
+      <c r="A5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8" t="s">
+      <c r="H5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8" t="s">
+      <c r="L5" s="9"/>
+      <c r="M5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="9">
+      <c r="N5" s="10">
         <v>9.0</v>
       </c>
-      <c r="P4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
-    </row>
-    <row r="5" ht="39.75" customHeight="1">
-      <c r="A5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
+      <c r="O5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+    </row>
+    <row r="6" ht="59.25" customHeight="1">
+      <c r="A6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="11">
-        <v>9.0</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-    </row>
-    <row r="6" ht="59.25" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+    </row>
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-    </row>
-    <row r="7" ht="48.0" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+    </row>
+    <row r="8" ht="26.25" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-    </row>
-    <row r="8" ht="26.25" customHeight="1">
-      <c r="A8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="9"/>
+      <c r="O9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+    </row>
+    <row r="11" ht="41.25" customHeight="1">
+      <c r="A11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-    </row>
-    <row r="11" ht="41.25" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="9"/>
+      <c r="O11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="8"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="7"/>
+      <c r="O12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" ht="38.25" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-    </row>
-    <row r="13" ht="38.25" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10" t="s">
+      <c r="G13" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="8"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="7"/>
+      <c r="O13" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+    </row>
+    <row r="14" ht="96.75" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-    </row>
-    <row r="14" ht="96.75" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10" t="s">
+      <c r="G14" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>85</v>
-      </c>
+      <c r="J14" s="9"/>
       <c r="K14" s="10"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="10" t="s">
+      <c r="M14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
     </row>
     <row r="15" ht="51.75" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10" t="s">
+      <c r="G15" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="10" t="s">
+      <c r="H15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="10" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10" t="s">
+      <c r="N15" s="9"/>
+      <c r="O15" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
-      <c r="AA15" s="12"/>
-    </row>
-    <row r="16" ht="49.5" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+    </row>
+    <row r="16" ht="77.25" customHeight="1">
+      <c r="A16" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10" t="s">
+      <c r="G16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10" t="s">
+      <c r="H16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10" t="s">
+      <c r="K16" s="9"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="N16" s="9"/>
+      <c r="O16" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P16" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-    </row>
-    <row r="17" ht="123.75" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+    </row>
+    <row r="17" ht="81.75" customHeight="1">
+      <c r="A17" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10" t="s">
+      <c r="G17" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="H17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="K17" s="9"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10" t="s">
+      <c r="N17" s="9"/>
+      <c r="O17" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="P17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+    </row>
+    <row r="18" ht="103.5" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-    </row>
-    <row r="18" ht="45.75" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="G18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" ht="51.75" customHeight="1">
+      <c r="A19" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-    </row>
-    <row r="19" ht="105.75" customHeight="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-    </row>
-    <row r="20" ht="105.75" customHeight="1">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-    </row>
-    <row r="21" ht="105.75" customHeight="1">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-    </row>
-    <row r="22" ht="105.75" customHeight="1">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-    </row>
-    <row r="23" ht="105.75" customHeight="1">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-    </row>
-    <row r="24" ht="105.75" customHeight="1">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-    </row>
-    <row r="25" ht="105.75" customHeight="1">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-    </row>
-    <row r="26" ht="105.75" customHeight="1">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+    </row>
+    <row r="20" ht="51.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+    </row>
+    <row r="21" ht="51.75" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+    </row>
+    <row r="22" ht="51.75" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="9"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+    </row>
+    <row r="23" ht="51.75" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+    </row>
+    <row r="24" ht="29.25" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+    </row>
+    <row r="25" ht="123.75" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+    </row>
+    <row r="26" ht="45.75" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
     </row>
     <row r="27" ht="105.75" customHeight="1">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
+      <c r="A27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
     </row>
     <row r="28" ht="105.75" customHeight="1">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
+      <c r="A28" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
     </row>
     <row r="29" ht="105.75" customHeight="1">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
+      <c r="A29" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
     </row>
     <row r="30" ht="105.75" customHeight="1">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
+      <c r="A30" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
     </row>
     <row r="31" ht="105.75" customHeight="1">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+      <c r="A31" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+    </row>
+    <row r="32" ht="237.0" customHeight="1">
+      <c r="A32" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+    </row>
+    <row r="33" ht="243.0" customHeight="1">
+      <c r="A33" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="12"/>
+      <c r="Z33" s="12"/>
+    </row>
+    <row r="34" ht="280.5" customHeight="1">
+      <c r="A34" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="12"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="12"/>
+      <c r="Z34" s="12"/>
+    </row>
+    <row r="35" ht="105.75" customHeight="1">
+      <c r="A35" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+    </row>
+    <row r="36" ht="105.75" customHeight="1">
+      <c r="A36" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="12"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+    </row>
+    <row r="37" ht="105.75" customHeight="1">
+      <c r="A37" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="12"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
+    </row>
+    <row r="38" ht="105.75" customHeight="1">
+      <c r="A38" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="12"/>
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="12"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+    </row>
+    <row r="39" ht="105.75" customHeight="1">
+      <c r="A39" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="12"/>
+      <c r="R39" s="12"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="12"/>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="12"/>
+    </row>
+    <row r="40" ht="105.75" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
+      <c r="R40" s="12"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="12"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+    </row>
+    <row r="41" ht="105.75" customHeight="1">
+      <c r="A41" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="12"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="12"/>
+      <c r="W41" s="12"/>
+      <c r="X41" s="12"/>
+      <c r="Y41" s="12"/>
+      <c r="Z41" s="12"/>
+    </row>
+    <row r="42" ht="105.75" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="12"/>
+      <c r="R42" s="12"/>
+      <c r="S42" s="12"/>
+      <c r="T42" s="12"/>
+      <c r="U42" s="12"/>
+      <c r="V42" s="12"/>
+      <c r="W42" s="12"/>
+      <c r="X42" s="12"/>
+      <c r="Y42" s="12"/>
+      <c r="Z42" s="12"/>
+    </row>
+    <row r="43" ht="105.75" customHeight="1">
+      <c r="A43" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="12"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="12"/>
+      <c r="U43" s="12"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="12"/>
+      <c r="Y43" s="12"/>
+      <c r="Z43" s="12"/>
+    </row>
+    <row r="44" ht="105.75" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="12"/>
+      <c r="R44" s="12"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="12"/>
+      <c r="U44" s="12"/>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
+      <c r="X44" s="12"/>
+      <c r="Y44" s="12"/>
+      <c r="Z44" s="12"/>
+    </row>
+    <row r="45" ht="105.75" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13"/>
+      <c r="R45" s="13"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="13"/>
+      <c r="U45" s="13"/>
+      <c r="V45" s="13"/>
+      <c r="W45" s="13"/>
+      <c r="X45" s="13"/>
+      <c r="Y45" s="13"/>
+      <c r="Z45" s="13"/>
+    </row>
+    <row r="46" ht="105.75" customHeight="1">
+      <c r="A46" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="13"/>
+      <c r="V46" s="13"/>
+      <c r="W46" s="13"/>
+      <c r="X46" s="13"/>
+      <c r="Y46" s="13"/>
+      <c r="Z46" s="13"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="13"/>
+      <c r="U47" s="13"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="13"/>
+      <c r="Z47" s="13"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="13"/>
+      <c r="Z48" s="13"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="13"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="Z49" s="13"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="13"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="13"/>
+      <c r="Z50" s="13"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="13"/>
+      <c r="Z51" s="13"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="13"/>
+      <c r="X52" s="13"/>
+      <c r="Y52" s="13"/>
+      <c r="Z52" s="13"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="13"/>
+      <c r="U53" s="13"/>
+      <c r="V53" s="13"/>
+      <c r="W53" s="13"/>
+      <c r="X53" s="13"/>
+      <c r="Y53" s="13"/>
+      <c r="Z53" s="13"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
+      <c r="U54" s="13"/>
+      <c r="V54" s="13"/>
+      <c r="W54" s="13"/>
+      <c r="X54" s="13"/>
+      <c r="Y54" s="13"/>
+      <c r="Z54" s="13"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="13"/>
+      <c r="U55" s="13"/>
+      <c r="V55" s="13"/>
+      <c r="W55" s="13"/>
+      <c r="X55" s="13"/>
+      <c r="Y55" s="13"/>
+      <c r="Z55" s="13"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="13"/>
+      <c r="U56" s="13"/>
+      <c r="V56" s="13"/>
+      <c r="W56" s="13"/>
+      <c r="X56" s="13"/>
+      <c r="Y56" s="13"/>
+      <c r="Z56" s="13"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="13"/>
+      <c r="U57" s="13"/>
+      <c r="V57" s="13"/>
+      <c r="W57" s="13"/>
+      <c r="X57" s="13"/>
+      <c r="Y57" s="13"/>
+      <c r="Z57" s="13"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="13"/>
+      <c r="Q58" s="13"/>
+      <c r="R58" s="13"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="13"/>
+      <c r="U58" s="13"/>
+      <c r="V58" s="13"/>
+      <c r="W58" s="13"/>
+      <c r="X58" s="13"/>
+      <c r="Y58" s="13"/>
+      <c r="Z58" s="13"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
+      <c r="Q59" s="13"/>
+      <c r="R59" s="13"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="13"/>
+      <c r="U59" s="13"/>
+      <c r="V59" s="13"/>
+      <c r="W59" s="13"/>
+      <c r="X59" s="13"/>
+      <c r="Y59" s="13"/>
+      <c r="Z59" s="13"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
+      <c r="Q60" s="13"/>
+      <c r="R60" s="13"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="13"/>
+      <c r="U60" s="13"/>
+      <c r="V60" s="13"/>
+      <c r="W60" s="13"/>
+      <c r="X60" s="13"/>
+      <c r="Y60" s="13"/>
+      <c r="Z60" s="13"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="13"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="13"/>
+      <c r="U61" s="13"/>
+      <c r="V61" s="13"/>
+      <c r="W61" s="13"/>
+      <c r="X61" s="13"/>
+      <c r="Y61" s="13"/>
+      <c r="Z61" s="13"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="13"/>
+      <c r="U62" s="13"/>
+      <c r="V62" s="13"/>
+      <c r="W62" s="13"/>
+      <c r="X62" s="13"/>
+      <c r="Y62" s="13"/>
+      <c r="Z62" s="13"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+      <c r="P63" s="13"/>
+      <c r="Q63" s="13"/>
+      <c r="R63" s="13"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="13"/>
+      <c r="U63" s="13"/>
+      <c r="V63" s="13"/>
+      <c r="W63" s="13"/>
+      <c r="X63" s="13"/>
+      <c r="Y63" s="13"/>
+      <c r="Z63" s="13"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="13"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="13"/>
+      <c r="Q64" s="13"/>
+      <c r="R64" s="13"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="13"/>
+      <c r="U64" s="13"/>
+      <c r="V64" s="13"/>
+      <c r="W64" s="13"/>
+      <c r="X64" s="13"/>
+      <c r="Y64" s="13"/>
+      <c r="Z64" s="13"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="13"/>
+      <c r="Q65" s="13"/>
+      <c r="R65" s="13"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="13"/>
+      <c r="U65" s="13"/>
+      <c r="V65" s="13"/>
+      <c r="W65" s="13"/>
+      <c r="X65" s="13"/>
+      <c r="Y65" s="13"/>
+      <c r="Z65" s="13"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="13"/>
+      <c r="Q66" s="13"/>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="13"/>
+      <c r="V66" s="13"/>
+      <c r="W66" s="13"/>
+      <c r="X66" s="13"/>
+      <c r="Y66" s="13"/>
+      <c r="Z66" s="13"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+      <c r="P67" s="13"/>
+      <c r="Q67" s="13"/>
+      <c r="R67" s="13"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="13"/>
+      <c r="U67" s="13"/>
+      <c r="V67" s="13"/>
+      <c r="W67" s="13"/>
+      <c r="X67" s="13"/>
+      <c r="Y67" s="13"/>
+      <c r="Z67" s="13"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="13"/>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="13"/>
+      <c r="U68" s="13"/>
+      <c r="V68" s="13"/>
+      <c r="W68" s="13"/>
+      <c r="X68" s="13"/>
+      <c r="Y68" s="13"/>
+      <c r="Z68" s="13"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+      <c r="P69" s="13"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="13"/>
+      <c r="U69" s="13"/>
+      <c r="V69" s="13"/>
+      <c r="W69" s="13"/>
+      <c r="X69" s="13"/>
+      <c r="Y69" s="13"/>
+      <c r="Z69" s="13"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+      <c r="P70" s="13"/>
+      <c r="Q70" s="13"/>
+      <c r="R70" s="13"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="13"/>
+      <c r="U70" s="13"/>
+      <c r="V70" s="13"/>
+      <c r="W70" s="13"/>
+      <c r="X70" s="13"/>
+      <c r="Y70" s="13"/>
+      <c r="Z70" s="13"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13"/>
+      <c r="P71" s="13"/>
+      <c r="Q71" s="13"/>
+      <c r="R71" s="13"/>
+      <c r="S71" s="13"/>
+      <c r="T71" s="13"/>
+      <c r="U71" s="13"/>
+      <c r="V71" s="13"/>
+      <c r="W71" s="13"/>
+      <c r="X71" s="13"/>
+      <c r="Y71" s="13"/>
+      <c r="Z71" s="13"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
+      <c r="R72" s="13"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="13"/>
+      <c r="U72" s="13"/>
+      <c r="V72" s="13"/>
+      <c r="W72" s="13"/>
+      <c r="X72" s="13"/>
+      <c r="Y72" s="13"/>
+      <c r="Z72" s="13"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="13"/>
+      <c r="U73" s="13"/>
+      <c r="V73" s="13"/>
+      <c r="W73" s="13"/>
+      <c r="X73" s="13"/>
+      <c r="Y73" s="13"/>
+      <c r="Z73" s="13"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="13"/>
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+      <c r="X74" s="13"/>
+      <c r="Y74" s="13"/>
+      <c r="Z74" s="13"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+      <c r="R75" s="13"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="13"/>
+      <c r="U75" s="13"/>
+      <c r="V75" s="13"/>
+      <c r="W75" s="13"/>
+      <c r="X75" s="13"/>
+      <c r="Y75" s="13"/>
+      <c r="Z75" s="13"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="13"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13"/>
+      <c r="P76" s="13"/>
+      <c r="Q76" s="13"/>
+      <c r="R76" s="13"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="13"/>
+      <c r="U76" s="13"/>
+      <c r="V76" s="13"/>
+      <c r="W76" s="13"/>
+      <c r="X76" s="13"/>
+      <c r="Y76" s="13"/>
+      <c r="Z76" s="13"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
+      <c r="P77" s="13"/>
+      <c r="Q77" s="13"/>
+      <c r="R77" s="13"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="13"/>
+      <c r="U77" s="13"/>
+      <c r="V77" s="13"/>
+      <c r="W77" s="13"/>
+      <c r="X77" s="13"/>
+      <c r="Y77" s="13"/>
+      <c r="Z77" s="13"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+      <c r="P78" s="13"/>
+      <c r="Q78" s="13"/>
+      <c r="R78" s="13"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="13"/>
+      <c r="U78" s="13"/>
+      <c r="V78" s="13"/>
+      <c r="W78" s="13"/>
+      <c r="X78" s="13"/>
+      <c r="Y78" s="13"/>
+      <c r="Z78" s="13"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="13"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13"/>
+      <c r="P79" s="13"/>
+      <c r="Q79" s="13"/>
+      <c r="R79" s="13"/>
+      <c r="S79" s="13"/>
+      <c r="T79" s="13"/>
+      <c r="U79" s="13"/>
+      <c r="V79" s="13"/>
+      <c r="W79" s="13"/>
+      <c r="X79" s="13"/>
+      <c r="Y79" s="13"/>
+      <c r="Z79" s="13"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="13"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13"/>
+      <c r="P80" s="13"/>
+      <c r="Q80" s="13"/>
+      <c r="R80" s="13"/>
+      <c r="S80" s="13"/>
+      <c r="T80" s="13"/>
+      <c r="U80" s="13"/>
+      <c r="V80" s="13"/>
+      <c r="W80" s="13"/>
+      <c r="X80" s="13"/>
+      <c r="Y80" s="13"/>
+      <c r="Z80" s="13"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="13"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13"/>
+      <c r="P81" s="13"/>
+      <c r="Q81" s="13"/>
+      <c r="R81" s="13"/>
+      <c r="S81" s="13"/>
+      <c r="T81" s="13"/>
+      <c r="U81" s="13"/>
+      <c r="V81" s="13"/>
+      <c r="W81" s="13"/>
+      <c r="X81" s="13"/>
+      <c r="Y81" s="13"/>
+      <c r="Z81" s="13"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="13"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+      <c r="P82" s="13"/>
+      <c r="Q82" s="13"/>
+      <c r="R82" s="13"/>
+      <c r="S82" s="13"/>
+      <c r="T82" s="13"/>
+      <c r="U82" s="13"/>
+      <c r="V82" s="13"/>
+      <c r="W82" s="13"/>
+      <c r="X82" s="13"/>
+      <c r="Y82" s="13"/>
+      <c r="Z82" s="13"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="13"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13"/>
+      <c r="P83" s="13"/>
+      <c r="Q83" s="13"/>
+      <c r="R83" s="13"/>
+      <c r="S83" s="13"/>
+      <c r="T83" s="13"/>
+      <c r="U83" s="13"/>
+      <c r="V83" s="13"/>
+      <c r="W83" s="13"/>
+      <c r="X83" s="13"/>
+      <c r="Y83" s="13"/>
+      <c r="Z83" s="13"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13"/>
+      <c r="P84" s="13"/>
+      <c r="Q84" s="13"/>
+      <c r="R84" s="13"/>
+      <c r="S84" s="13"/>
+      <c r="T84" s="13"/>
+      <c r="U84" s="13"/>
+      <c r="V84" s="13"/>
+      <c r="W84" s="13"/>
+      <c r="X84" s="13"/>
+      <c r="Y84" s="13"/>
+      <c r="Z84" s="13"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="13"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="13"/>
+      <c r="L85" s="13"/>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="13"/>
+      <c r="P85" s="13"/>
+      <c r="Q85" s="13"/>
+      <c r="R85" s="13"/>
+      <c r="S85" s="13"/>
+      <c r="T85" s="13"/>
+      <c r="U85" s="13"/>
+      <c r="V85" s="13"/>
+      <c r="W85" s="13"/>
+      <c r="X85" s="13"/>
+      <c r="Y85" s="13"/>
+      <c r="Z85" s="13"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+      <c r="P86" s="13"/>
+      <c r="Q86" s="13"/>
+      <c r="R86" s="13"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="13"/>
+      <c r="U86" s="13"/>
+      <c r="V86" s="13"/>
+      <c r="W86" s="13"/>
+      <c r="X86" s="13"/>
+      <c r="Y86" s="13"/>
+      <c r="Z86" s="13"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="13"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13"/>
+      <c r="O87" s="13"/>
+      <c r="P87" s="13"/>
+      <c r="Q87" s="13"/>
+      <c r="R87" s="13"/>
+      <c r="S87" s="13"/>
+      <c r="T87" s="13"/>
+      <c r="U87" s="13"/>
+      <c r="V87" s="13"/>
+      <c r="W87" s="13"/>
+      <c r="X87" s="13"/>
+      <c r="Y87" s="13"/>
+      <c r="Z87" s="13"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="13"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="13"/>
+      <c r="L88" s="13"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13"/>
+      <c r="P88" s="13"/>
+      <c r="Q88" s="13"/>
+      <c r="R88" s="13"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="13"/>
+      <c r="U88" s="13"/>
+      <c r="V88" s="13"/>
+      <c r="W88" s="13"/>
+      <c r="X88" s="13"/>
+      <c r="Y88" s="13"/>
+      <c r="Z88" s="13"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="13"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13"/>
+      <c r="P89" s="13"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="13"/>
+      <c r="S89" s="13"/>
+      <c r="T89" s="13"/>
+      <c r="U89" s="13"/>
+      <c r="V89" s="13"/>
+      <c r="W89" s="13"/>
+      <c r="X89" s="13"/>
+      <c r="Y89" s="13"/>
+      <c r="Z89" s="13"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="13"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="13"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="13"/>
+      <c r="U90" s="13"/>
+      <c r="V90" s="13"/>
+      <c r="W90" s="13"/>
+      <c r="X90" s="13"/>
+      <c r="Y90" s="13"/>
+      <c r="Z90" s="13"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="13"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+      <c r="K91" s="13"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
+      <c r="N91" s="13"/>
+      <c r="O91" s="13"/>
+      <c r="P91" s="13"/>
+      <c r="Q91" s="13"/>
+      <c r="R91" s="13"/>
+      <c r="S91" s="13"/>
+      <c r="T91" s="13"/>
+      <c r="U91" s="13"/>
+      <c r="V91" s="13"/>
+      <c r="W91" s="13"/>
+      <c r="X91" s="13"/>
+      <c r="Y91" s="13"/>
+      <c r="Z91" s="13"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="13"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
+      <c r="K92" s="13"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
+      <c r="N92" s="13"/>
+      <c r="O92" s="13"/>
+      <c r="P92" s="13"/>
+      <c r="Q92" s="13"/>
+      <c r="R92" s="13"/>
+      <c r="S92" s="13"/>
+      <c r="T92" s="13"/>
+      <c r="U92" s="13"/>
+      <c r="V92" s="13"/>
+      <c r="W92" s="13"/>
+      <c r="X92" s="13"/>
+      <c r="Y92" s="13"/>
+      <c r="Z92" s="13"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="13"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="13"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="13"/>
+      <c r="O93" s="13"/>
+      <c r="P93" s="13"/>
+      <c r="Q93" s="13"/>
+      <c r="R93" s="13"/>
+      <c r="S93" s="13"/>
+      <c r="T93" s="13"/>
+      <c r="U93" s="13"/>
+      <c r="V93" s="13"/>
+      <c r="W93" s="13"/>
+      <c r="X93" s="13"/>
+      <c r="Y93" s="13"/>
+      <c r="Z93" s="13"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="13"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="13"/>
+      <c r="K94" s="13"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
+      <c r="N94" s="13"/>
+      <c r="O94" s="13"/>
+      <c r="P94" s="13"/>
+      <c r="Q94" s="13"/>
+      <c r="R94" s="13"/>
+      <c r="S94" s="13"/>
+      <c r="T94" s="13"/>
+      <c r="U94" s="13"/>
+      <c r="V94" s="13"/>
+      <c r="W94" s="13"/>
+      <c r="X94" s="13"/>
+      <c r="Y94" s="13"/>
+      <c r="Z94" s="13"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="13"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="13"/>
+      <c r="J95" s="13"/>
+      <c r="K95" s="13"/>
+      <c r="L95" s="13"/>
+      <c r="M95" s="13"/>
+      <c r="N95" s="13"/>
+      <c r="O95" s="13"/>
+      <c r="P95" s="13"/>
+      <c r="Q95" s="13"/>
+      <c r="R95" s="13"/>
+      <c r="S95" s="13"/>
+      <c r="T95" s="13"/>
+      <c r="U95" s="13"/>
+      <c r="V95" s="13"/>
+      <c r="W95" s="13"/>
+      <c r="X95" s="13"/>
+      <c r="Y95" s="13"/>
+      <c r="Z95" s="13"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="13"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
+      <c r="K96" s="13"/>
+      <c r="L96" s="13"/>
+      <c r="M96" s="13"/>
+      <c r="N96" s="13"/>
+      <c r="O96" s="13"/>
+      <c r="P96" s="13"/>
+      <c r="Q96" s="13"/>
+      <c r="R96" s="13"/>
+      <c r="S96" s="13"/>
+      <c r="T96" s="13"/>
+      <c r="U96" s="13"/>
+      <c r="V96" s="13"/>
+      <c r="W96" s="13"/>
+      <c r="X96" s="13"/>
+      <c r="Y96" s="13"/>
+      <c r="Z96" s="13"/>
+    </row>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -2983,7 +5208,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -3887,7 +3887,7 @@
       <c r="Z49" s="17"/>
       <c r="AA49" s="17"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="35.25" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>351</v>
       </c>

--- a/main/upload/upload.xlsx
+++ b/main/upload/upload.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="366">
   <si>
     <r>
       <rPr>
@@ -106,61 +106,64 @@
     <t>Центробежный насос для перекачки пресной воды без абразивных и волокнистых частиц из колодцев, резервуаров и открытых водоёмов. Подходит для полива, водоснабжения дома, повышения давления в системе. После первичного заполнения работает в режиме самовсасывания. Эксплуатация: от +5°С до +35°С, влажность до 98%. Рекомендуемый диаметр шлангов (труб) — не менее 1" (25 мм).</t>
   </si>
   <si>
+    <t>poverhnostnyie-sadovyie-nasosyi-.png</t>
+  </si>
+  <si>
+    <t>QB60.png</t>
+  </si>
+  <si>
+    <t>QB60-1.png,QB60-2.png,QB60-3.png</t>
+  </si>
+  <si>
+    <t>ENSI QB60, ENSI QB70</t>
+  </si>
+  <si>
+    <t>0.37, 0.55</t>
+  </si>
+  <si>
+    <t>220В 50Гц</t>
+  </si>
+  <si>
+    <t>35, 50</t>
+  </si>
+  <si>
+    <t>1" × 1"</t>
+  </si>
+  <si>
+    <t>Насосы серии JS</t>
+  </si>
+  <si>
+    <t>Центробежные поверхностные насосы серии JS с внутренним эжектором предназначены для подачи чистой воды из скважин, колодцев и других источников, а также для работы в автоматических системах водоснабжения. Допустимы частицы до 1 мм, не более 100 г/м³. Температура воды: от +1°С до +35°С.</t>
+  </si>
+  <si>
+    <t>js100 m.png</t>
+  </si>
+  <si>
+    <t>js100 m.png,js100 m02.png,js100 m03.png</t>
+  </si>
+  <si>
+    <t>ENSI JS-60, ENSI JS-80, ENSI JS-100</t>
+  </si>
+  <si>
+    <t>0.55, 0.75, 1.1</t>
+  </si>
+  <si>
+    <t>42, 45, 50</t>
+  </si>
+  <si>
+    <t>38, 42, 50</t>
+  </si>
+  <si>
+    <t>Насосы серии JET-S</t>
+  </si>
+  <si>
+    <t>Центробежные поверхностные насосы  серии JET S - это центробежные поверхностные насосы c внутренним эжектором, применяются для подачи чистой воды из скважин, колодцев и других источников водоснабжения, кроме того они могут быть использованы в автоматических системах водоснабжения.</t>
+  </si>
+  <si>
     <t xml:space="preserve">poverhnostnyie-sadovyie-nasosyi-.png
 </t>
   </si>
   <si>
-    <t>QB60.png</t>
-  </si>
-  <si>
-    <t>QB60-1.png,QB60-2.png,QB60-3.png</t>
-  </si>
-  <si>
-    <t>ENSI QB60, ENSI QB70</t>
-  </si>
-  <si>
-    <t>0.37, 0.55</t>
-  </si>
-  <si>
-    <t>220В 50Гц</t>
-  </si>
-  <si>
-    <t>35, 50</t>
-  </si>
-  <si>
-    <t>1" × 1"</t>
-  </si>
-  <si>
-    <t>Насосы серии JS</t>
-  </si>
-  <si>
-    <t>Центробежные поверхностные насосы серии JS с внутренним эжектором предназначены для подачи чистой воды из скважин, колодцев и других источников, а также для работы в автоматических системах водоснабжения. Допустимы частицы до 1 мм, не более 100 г/м³. Температура воды: от +1°С до +35°С.</t>
-  </si>
-  <si>
-    <t>js100 m.png</t>
-  </si>
-  <si>
-    <t>js100 m.png,js100 m02.png,js100 m03.png</t>
-  </si>
-  <si>
-    <t>ENSI JS-60, ENSI JS-80, ENSI JS-100</t>
-  </si>
-  <si>
-    <t>0.55, 0.75, 1.1</t>
-  </si>
-  <si>
-    <t>42, 45, 50</t>
-  </si>
-  <si>
-    <t>38, 42, 50</t>
-  </si>
-  <si>
-    <t>Насосы серии JET-S</t>
-  </si>
-  <si>
-    <t>Центробежные поверхностные насосы  серии JET S - это центробежные поверхностные насосы c внутренним эжектором, применяются для подачи чистой воды из скважин, колодцев и других источников водоснабжения, кроме того они могут быть использованы в автоматических системах водоснабжения.</t>
-  </si>
-  <si>
     <t>JET-S 60.png</t>
   </si>
   <si>
@@ -177,39 +180,36 @@
   </si>
   <si>
     <t>Погружной дренажный насос с поплавковым выключателем предназначен для откачивания и перекачивания грязной воды. Подходит для полива, осушения затопленных участков и емкостей, регулирования уровня воды в водоёмах, а также для аварийной откачки. Оснащён поплавковым механизмом автоматического отключения при понижении уровня воды и герметичным корпусом, устойчивым к коррозии и воздействию ультрафиолета.</t>
-  </si>
-  <si>
-    <t>Погружные (Дренажные) насосы.png</t>
-  </si>
-  <si>
-    <t>KQ1100B2.png</t>
-  </si>
-  <si>
-    <t>KQ1100B2.png,KQ1100B2-1.png,KQ1100B2-3.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENSI Q250 3, ENSI Q350 14-1, ENSI Q400 11, ENSI Q400 3А, ENSI Q400 51R, ENSI Q750 B11, ENSI Q750 B3, ENSI Q750 B54R, ENSI Q1100 B54R, ENSI Q1300 B101, ENSI Q1000 103-4Р  </t>
-  </si>
-  <si>
-    <t>0.25, 0.35, 0.4, 0.4, 0.4, 0.75, 0.75, 0.75, 1.1, 1.3, 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6, 10, 8, 8, 6.5, 8, 8,8, 10.5, 11, 40 </t>
-  </si>
-  <si>
-    <t>1", 11/4"</t>
-  </si>
-  <si>
-    <t>Насосы серии QDX</t>
-  </si>
-  <si>
-    <t>Погружные  дренажные насосы серии QDX предназначены,  для перекачивания чистой и загрязненной воды(max. размер частиц 3мм) из водоемов, колодцев, подвалов, прудов, бассейнов, с автоматическим включением и отключением насоса при помощи поплавкового выключателя. Серия QDX выполнена полностью из металла, включая рабочее колесо и его защиту.</t>
   </si>
   <si>
     <t xml:space="preserve">pogruzhnyie-drenazhnyie-nasosyi.png
 </t>
   </si>
   <si>
+    <t>KQ1100B2.png</t>
+  </si>
+  <si>
+    <t>KQ1100B2.png,KQ1100B2-1.png,KQ1100B2-3.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENSI Q250 3, ENSI Q350 14-1, ENSI Q400 11, ENSI Q400 3А, ENSI Q400 51R, ENSI Q750 B11, ENSI Q750 B3, ENSI Q750 B54R, ENSI Q1100 B54R, ENSI Q1300 B101, ENSI Q1000 103-4Р  </t>
+  </si>
+  <si>
+    <t>0.25, 0.35, 0.4, 0.4, 0.4, 0.75, 0.75, 0.75, 1.1, 1.3, 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6, 10, 8, 8, 6.5, 8, 8,8, 10.5, 11, 40 </t>
+  </si>
+  <si>
+    <t>1", 11/4"</t>
+  </si>
+  <si>
+    <t>Насосы серии QDX</t>
+  </si>
+  <si>
+    <t>Погружные  дренажные насосы серии QDX предназначены,  для перекачивания чистой и загрязненной воды(max. размер частиц 3мм) из водоемов, колодцев, подвалов, прудов, бассейнов, с автоматическим включением и отключением насоса при помощи поплавкового выключателя. Серия QDX выполнена полностью из металла, включая рабочее колесо и его защиту.</t>
+  </si>
+  <si>
     <t>QDX.png</t>
   </si>
   <si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Погружной дренажный насоссерии V  предназначен для откачивания грязной и сливной воды из подвалов, колодцев, ям, резервуаров и затопленных участков. Оснащён поплавковым выключателем для автоматического включения и отключения в зависимости от уровня воды. Корпус выполнен из прочных материалов, устойчивых к коррозии, что обеспечивает надёжную и долговечную работу в бытовых и хозяйственных условиях.</t>
+  </si>
+  <si>
+    <t>pogruzhnyie-drenazhnyie-nasosyi.png</t>
   </si>
   <si>
     <t>Насосы серии V.png</t>
@@ -427,7 +430,7 @@
     <t>Насосы серии GPD</t>
   </si>
   <si>
-    <t>Циркуляционные насосы с мокрым ротором.png</t>
+    <t>tsirkulyatsionnyie-nasosyi-s-mokryim-rotorom.png</t>
   </si>
   <si>
     <t>Насосы серии GPD.png</t>
@@ -649,7 +652,7 @@
     <t>Насосы серии HMC</t>
   </si>
   <si>
-    <t>Горизонтальные многоступенчатые насосы.png</t>
+    <t>gorizontalnyie-mnogostupenchatyie-nasosyi.png</t>
   </si>
   <si>
     <t>Насосы серии HMC.png</t>
@@ -736,7 +739,8 @@
     <t>Насосы серии  MP (Профи)</t>
   </si>
   <si>
-    <t>Канализационные установки.png</t>
+    <t xml:space="preserve">kanalizatsionnyie-ustanovki.png
+</t>
   </si>
   <si>
     <t>Насосы серии  MP (Профи).png</t>
@@ -773,6 +777,10 @@
   </si>
   <si>
     <t>Жироуловитель (или жироотделитель, сепаратор жира) — это устройство для очистки сточных вод от жиров и масел, которое предотвращает засоры канализации и неприятные запахи, задерживая жир и частицы пищи в специальной камере благодаря разнице плотности жира (всплывает) и воды. Они устанавливаются как в быту (под мойку), так и на промышленных кухнях, кафе, ресторанах, и бывают компактными или крупными.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zhirouloviteli.png
+</t>
   </si>
   <si>
     <t>Жироуловители.png</t>
@@ -792,7 +800,8 @@
     <t>Насосы серии PT</t>
   </si>
   <si>
-    <t>Насосы In-Line ( в линию) .png</t>
+    <t xml:space="preserve">nasosyi-in-line--v-liniyu-.png
+</t>
   </si>
   <si>
     <t>Насосы серии PT.png</t>
@@ -846,7 +855,7 @@
     <t>Насосы серии PST</t>
   </si>
   <si>
-    <t>Консольно-моноблочные насосы .png</t>
+    <t>konsolno-monoblochnyie-nasosyi-.png</t>
   </si>
   <si>
     <t>Насосы серии PST.png</t>
@@ -873,7 +882,8 @@
     <t>Насосы серии CDL</t>
   </si>
   <si>
-    <t>Вертикальные многоступенчатые насосы.png</t>
+    <t xml:space="preserve">vertikalnyie-mnogostupenchatyie-nasosyi.png
+</t>
   </si>
   <si>
     <t>Насосы серии CDL.png</t>
@@ -903,7 +913,7 @@
     <t>Ручные</t>
   </si>
   <si>
-    <t>Опрессовочные испытательные насосы.png</t>
+    <t>opressovochnyie-ispyitatelnyie-nasosyi.png</t>
   </si>
   <si>
     <t>НИР 25-.png</t>
@@ -927,7 +937,7 @@
     <t xml:space="preserve">Кран ручной топливораздаточный </t>
   </si>
   <si>
-    <t>Насосы и оборудование для ГСМ.png</t>
+    <t>nasosyi-i-oborudovanie-dlya-gsm.png</t>
   </si>
   <si>
     <t>Кран ручной топливораздаточный.png</t>
@@ -990,7 +1000,7 @@
     <t>Гидроаккумуляторы</t>
   </si>
   <si>
-    <t>Гидроаккумуляторы и расширительные баки.png</t>
+    <t>gidroakkumulyatoryi-i-rasshiritelnyie-baki.png</t>
   </si>
   <si>
     <t>Гидроаккумуляторы.png</t>
@@ -1041,7 +1051,7 @@
     <t>Механические реле давления</t>
   </si>
   <si>
-    <t>Автоматика и управление.png</t>
+    <t>avtomatika-i-upravlenie.png</t>
   </si>
   <si>
     <t>Механические реле давления.png</t>
@@ -1095,7 +1105,7 @@
     <t>Нет подкатегории</t>
   </si>
   <si>
-    <t>Аксессуары и комплектующие .png</t>
+    <t>aksessuaryi-i-komplektuyuschie-.png</t>
   </si>
   <si>
     <t>Аксессуары фитинги.png</t>
@@ -1110,7 +1120,7 @@
     <t>Нет подкатегории1</t>
   </si>
   <si>
-    <t>Ручные насосы.png</t>
+    <t>ruchnyie-nasosyi.png</t>
   </si>
   <si>
     <t>Ручные насосы1.png</t>
@@ -1128,7 +1138,7 @@
     <t>Нет подкатегории2</t>
   </si>
   <si>
-    <t>Мотопомпы.png</t>
+    <t>motopompyi.png</t>
   </si>
   <si>
     <t>Мотопомпы разные.png</t>
@@ -1692,16 +1702,16 @@
         <v>38</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>34</v>
@@ -1738,28 +1748,28 @@
     </row>
     <row r="6" ht="59.25" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="12" t="s">
         <v>45</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>46</v>
+      </c>
       <c r="E6" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>26</v>
@@ -1769,11 +1779,11 @@
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
@@ -1789,16 +1799,16 @@
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>55</v>
@@ -1840,7 +1850,7 @@
     </row>
     <row r="8" ht="26.25" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>60</v>
@@ -1849,35 +1859,35 @@
         <v>61</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8" s="12"/>
       <c r="P8" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
@@ -1893,44 +1903,44 @@
     </row>
     <row r="9" ht="31.5" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" s="12"/>
       <c r="P9" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
@@ -1946,44 +1956,44 @@
     </row>
     <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
       <c r="M10" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
@@ -1999,44 +2009,44 @@
     </row>
     <row r="11" ht="41.25" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="16"/>
       <c r="N11" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O11" s="12"/>
       <c r="P11" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
@@ -2052,44 +2062,44 @@
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -2105,44 +2115,44 @@
     </row>
     <row r="13" ht="38.25" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="16"/>
       <c r="N13" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O13" s="10"/>
       <c r="P13" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
@@ -2158,44 +2168,44 @@
     </row>
     <row r="14" ht="96.75" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="15"/>
       <c r="M14" s="16"/>
       <c r="N14" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O14" s="12"/>
       <c r="P14" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
@@ -2211,44 +2221,44 @@
     </row>
     <row r="15" ht="51.75" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="16"/>
       <c r="N15" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O15" s="12"/>
       <c r="P15" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q15" s="16"/>
       <c r="R15" s="16"/>
@@ -2264,47 +2274,47 @@
     </row>
     <row r="16" ht="77.25" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="16"/>
       <c r="N16" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O16" s="12"/>
       <c r="P16" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
@@ -2319,47 +2329,47 @@
     </row>
     <row r="17" ht="108.0" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="16"/>
       <c r="N17" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O17" s="12"/>
       <c r="P17" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
@@ -2374,28 +2384,28 @@
     </row>
     <row r="18" ht="103.5" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>26</v>
@@ -2403,18 +2413,18 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M18" s="16"/>
       <c r="N18" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="R18" s="16"/>
       <c r="S18" s="16"/>
@@ -2429,47 +2439,47 @@
     </row>
     <row r="19" ht="51.75" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="16"/>
       <c r="N19" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O19" s="12"/>
       <c r="P19" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R19" s="16"/>
       <c r="S19" s="16"/>
@@ -2484,47 +2494,47 @@
     </row>
     <row r="20" ht="51.75" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="16"/>
       <c r="N20" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O20" s="12"/>
       <c r="P20" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
@@ -2539,47 +2549,47 @@
     </row>
     <row r="21" ht="51.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="16"/>
       <c r="N21" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O21" s="12"/>
       <c r="P21" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
@@ -2594,47 +2604,47 @@
     </row>
     <row r="22" ht="51.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="16"/>
       <c r="N22" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O22" s="12"/>
       <c r="P22" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
@@ -2649,47 +2659,47 @@
     </row>
     <row r="23" ht="51.75" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>127</v>
+        <v>88</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="16"/>
       <c r="N23" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O23" s="12"/>
       <c r="P23" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q23" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
@@ -2704,28 +2714,28 @@
     </row>
     <row r="24" ht="29.25" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>201</v>
+        <v>88</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>202</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>26</v>
@@ -2733,17 +2743,17 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
       <c r="L24" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q24" s="12"/>
       <c r="R24" s="12"/>
@@ -2759,46 +2769,46 @@
     </row>
     <row r="25" ht="123.75" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>201</v>
+        <v>88</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>202</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
@@ -2814,46 +2824,46 @@
     </row>
     <row r="26" ht="45.75" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>201</v>
+        <v>88</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>202</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K26" s="12"/>
       <c r="L26" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
@@ -2869,25 +2879,25 @@
     </row>
     <row r="27" ht="105.75" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>230</v>
+        <v>88</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
@@ -2912,25 +2922,25 @@
     </row>
     <row r="28" ht="105.75" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>230</v>
+        <v>88</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
@@ -2955,25 +2965,25 @@
     </row>
     <row r="29" ht="105.75" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>230</v>
+        <v>88</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
@@ -2998,25 +3008,25 @@
     </row>
     <row r="30" ht="105.75" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D30" s="12" t="s">
         <v>243</v>
       </c>
+      <c r="D30" s="14" t="s">
+        <v>244</v>
+      </c>
       <c r="E30" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
@@ -3041,45 +3051,45 @@
     </row>
     <row r="31" ht="105.75" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>248</v>
+        <v>88</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
@@ -3094,45 +3104,45 @@
     </row>
     <row r="32" ht="237.0" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>248</v>
+        <v>88</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
       <c r="M32" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
       <c r="P32" s="12"/>
       <c r="Q32" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
@@ -3147,38 +3157,38 @@
     </row>
     <row r="33" ht="243.0" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>266</v>
+        <v>88</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>268</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
       <c r="K33" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L33" s="12"/>
       <c r="M33" s="12"/>
       <c r="N33" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
@@ -3196,40 +3206,40 @@
     </row>
     <row r="34" ht="280.5" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>275</v>
+        <v>88</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>277</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
       <c r="K34" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
@@ -3247,22 +3257,22 @@
     </row>
     <row r="35" ht="105.75" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>285</v>
+        <v>88</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
@@ -3288,25 +3298,25 @@
     </row>
     <row r="36" ht="105.75" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B36" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>285</v>
-      </c>
       <c r="E36" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
@@ -3331,25 +3341,25 @@
     </row>
     <row r="37" ht="105.75" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>293</v>
+        <v>88</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
@@ -3374,25 +3384,25 @@
     </row>
     <row r="38" ht="105.75" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>293</v>
+        <v>88</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
@@ -3417,38 +3427,38 @@
     </row>
     <row r="39" ht="105.75" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>293</v>
+        <v>88</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
       <c r="L39" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O39" s="12"/>
       <c r="P39" s="12">
@@ -3468,25 +3478,25 @@
     </row>
     <row r="40" ht="105.75" customHeight="1">
       <c r="A40" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>293</v>
+        <v>88</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
@@ -3511,25 +3521,25 @@
     </row>
     <row r="41" ht="105.75" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>314</v>
+        <v>88</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>316</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
@@ -3554,25 +3564,25 @@
     </row>
     <row r="42" ht="105.75" customHeight="1">
       <c r="A42" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>314</v>
+        <v>88</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>316</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
@@ -3597,25 +3607,25 @@
     </row>
     <row r="43" ht="105.75" customHeight="1">
       <c r="A43" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>314</v>
+        <v>88</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>316</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
@@ -3640,25 +3650,25 @@
     </row>
     <row r="44" ht="105.75" customHeight="1">
       <c r="A44" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>314</v>
+        <v>88</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>316</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
@@ -3683,25 +3693,25 @@
     </row>
     <row r="45" ht="105.75" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>331</v>
+        <v>88</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="12" t="s">
@@ -3728,25 +3738,25 @@
     </row>
     <row r="46" ht="105.75" customHeight="1">
       <c r="A46" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>331</v>
+        <v>88</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
@@ -3771,25 +3781,25 @@
     </row>
     <row r="47" ht="105.75" customHeight="1">
       <c r="A47" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>331</v>
+        <v>88</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="12"/>
@@ -3814,25 +3824,25 @@
     </row>
     <row r="48" ht="105.75" customHeight="1">
       <c r="A48" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>331</v>
+        <v>88</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
@@ -3857,25 +3867,25 @@
     </row>
     <row r="49" ht="105.75" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>349</v>
+        <v>88</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>351</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
@@ -3900,25 +3910,25 @@
     </row>
     <row r="50" ht="35.25" customHeight="1">
       <c r="A50" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>354</v>
+        <v>88</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>356</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
@@ -3943,25 +3953,25 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>360</v>
+        <v>88</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>362</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
